--- a/doc/result/감리정본/[지재원] AI 영업비밀관리시스템 구축 WBS.xlsx
+++ b/doc/result/감리정본/[지재원] AI 영업비밀관리시스템 구축 WBS.xlsx
@@ -2567,603 +2567,607 @@
           <t>[지재원] AI 영업비밀관리시스템 구축 WBS</t>
         </is>
       </c>
-      <c r="C1" s="175" t="n"/>
-      <c r="D1" s="175" t="n"/>
-      <c r="E1" s="175" t="n"/>
-      <c r="F1" s="175" t="n"/>
+      <c r="C1" s="359" t="n"/>
+      <c r="D1" s="359" t="n"/>
+      <c r="E1" s="359" t="n"/>
+      <c r="F1" s="359" t="n"/>
       <c r="G1" s="414" t="inlineStr">
         <is>
           <t>6월</t>
         </is>
       </c>
-      <c r="H1" s="176" t="n"/>
-      <c r="I1" s="176" t="n"/>
-      <c r="J1" s="176" t="n"/>
-      <c r="K1" s="176" t="n"/>
-      <c r="L1" s="176" t="n"/>
-      <c r="M1" s="176" t="n"/>
-      <c r="N1" s="176" t="n"/>
-      <c r="O1" s="176" t="n"/>
-      <c r="P1" s="176" t="n"/>
-      <c r="Q1" s="176" t="n"/>
-      <c r="R1" s="176" t="n"/>
-      <c r="S1" s="176" t="n"/>
-      <c r="T1" s="176" t="n"/>
-      <c r="U1" s="176" t="n"/>
-      <c r="V1" s="176" t="n"/>
-      <c r="W1" s="176" t="n"/>
-      <c r="X1" s="176" t="n"/>
-      <c r="Y1" s="176" t="n"/>
-      <c r="Z1" s="176" t="n"/>
-      <c r="AA1" s="176" t="n"/>
-      <c r="AB1" s="176" t="n"/>
-      <c r="AC1" s="176" t="n"/>
-      <c r="AD1" s="176" t="n"/>
-      <c r="AE1" s="176" t="n"/>
-      <c r="AF1" s="176" t="n"/>
-      <c r="AG1" s="176" t="n"/>
-      <c r="AH1" s="176" t="n"/>
-      <c r="AI1" s="177" t="n"/>
+      <c r="H1" s="361" t="n"/>
+      <c r="I1" s="361" t="n"/>
+      <c r="J1" s="361" t="n"/>
+      <c r="K1" s="361" t="n"/>
+      <c r="L1" s="361" t="n"/>
+      <c r="M1" s="361" t="n"/>
+      <c r="N1" s="361" t="n"/>
+      <c r="O1" s="361" t="n"/>
+      <c r="P1" s="361" t="n"/>
+      <c r="Q1" s="361" t="n"/>
+      <c r="R1" s="361" t="n"/>
+      <c r="S1" s="361" t="n"/>
+      <c r="T1" s="361" t="n"/>
+      <c r="U1" s="361" t="n"/>
+      <c r="V1" s="361" t="n"/>
+      <c r="W1" s="361" t="n"/>
+      <c r="X1" s="361" t="n"/>
+      <c r="Y1" s="361" t="n"/>
+      <c r="Z1" s="361" t="n"/>
+      <c r="AA1" s="361" t="n"/>
+      <c r="AB1" s="361" t="n"/>
+      <c r="AC1" s="361" t="n"/>
+      <c r="AD1" s="361" t="n"/>
+      <c r="AE1" s="361" t="n"/>
+      <c r="AF1" s="361" t="n"/>
+      <c r="AG1" s="361" t="n"/>
+      <c r="AH1" s="361" t="n"/>
+      <c r="AI1" s="362" t="n"/>
       <c r="AJ1" s="414" t="inlineStr">
         <is>
           <t>7월</t>
         </is>
       </c>
-      <c r="AK1" s="176" t="n"/>
-      <c r="AL1" s="176" t="n"/>
-      <c r="AM1" s="176" t="n"/>
-      <c r="AN1" s="176" t="n"/>
-      <c r="AO1" s="176" t="n"/>
-      <c r="AP1" s="176" t="n"/>
-      <c r="AQ1" s="176" t="n"/>
-      <c r="AR1" s="176" t="n"/>
-      <c r="AS1" s="176" t="n"/>
-      <c r="AT1" s="176" t="n"/>
-      <c r="AU1" s="176" t="n"/>
-      <c r="AV1" s="176" t="n"/>
-      <c r="AW1" s="176" t="n"/>
-      <c r="AX1" s="176" t="n"/>
-      <c r="AY1" s="176" t="n"/>
-      <c r="AZ1" s="176" t="n"/>
-      <c r="BA1" s="176" t="n"/>
-      <c r="BB1" s="176" t="n"/>
-      <c r="BC1" s="176" t="n"/>
-      <c r="BD1" s="176" t="n"/>
-      <c r="BE1" s="176" t="n"/>
-      <c r="BF1" s="176" t="n"/>
-      <c r="BG1" s="176" t="n"/>
-      <c r="BH1" s="176" t="n"/>
-      <c r="BI1" s="176" t="n"/>
-      <c r="BJ1" s="176" t="n"/>
-      <c r="BK1" s="176" t="n"/>
-      <c r="BL1" s="176" t="n"/>
-      <c r="BM1" s="176" t="n"/>
-      <c r="BN1" s="177" t="n"/>
+      <c r="AK1" s="361" t="n"/>
+      <c r="AL1" s="361" t="n"/>
+      <c r="AM1" s="361" t="n"/>
+      <c r="AN1" s="361" t="n"/>
+      <c r="AO1" s="361" t="n"/>
+      <c r="AP1" s="361" t="n"/>
+      <c r="AQ1" s="361" t="n"/>
+      <c r="AR1" s="361" t="n"/>
+      <c r="AS1" s="361" t="n"/>
+      <c r="AT1" s="361" t="n"/>
+      <c r="AU1" s="361" t="n"/>
+      <c r="AV1" s="361" t="n"/>
+      <c r="AW1" s="361" t="n"/>
+      <c r="AX1" s="361" t="n"/>
+      <c r="AY1" s="361" t="n"/>
+      <c r="AZ1" s="361" t="n"/>
+      <c r="BA1" s="361" t="n"/>
+      <c r="BB1" s="361" t="n"/>
+      <c r="BC1" s="361" t="n"/>
+      <c r="BD1" s="361" t="n"/>
+      <c r="BE1" s="361" t="n"/>
+      <c r="BF1" s="361" t="n"/>
+      <c r="BG1" s="361" t="n"/>
+      <c r="BH1" s="361" t="n"/>
+      <c r="BI1" s="361" t="n"/>
+      <c r="BJ1" s="361" t="n"/>
+      <c r="BK1" s="361" t="n"/>
+      <c r="BL1" s="361" t="n"/>
+      <c r="BM1" s="361" t="n"/>
+      <c r="BN1" s="362" t="n"/>
       <c r="BO1" s="414" t="inlineStr">
         <is>
           <t>8월</t>
         </is>
       </c>
-      <c r="BP1" s="176" t="n"/>
-      <c r="BQ1" s="176" t="n"/>
-      <c r="BR1" s="176" t="n"/>
-      <c r="BS1" s="176" t="n"/>
-      <c r="BT1" s="176" t="n"/>
-      <c r="BU1" s="176" t="n"/>
-      <c r="BV1" s="176" t="n"/>
-      <c r="BW1" s="176" t="n"/>
-      <c r="BX1" s="176" t="n"/>
-      <c r="BY1" s="176" t="n"/>
-      <c r="BZ1" s="176" t="n"/>
-      <c r="CA1" s="176" t="n"/>
-      <c r="CB1" s="176" t="n"/>
-      <c r="CC1" s="176" t="n"/>
-      <c r="CD1" s="176" t="n"/>
-      <c r="CE1" s="176" t="n"/>
-      <c r="CF1" s="176" t="n"/>
-      <c r="CG1" s="176" t="n"/>
-      <c r="CH1" s="176" t="n"/>
-      <c r="CI1" s="176" t="n"/>
-      <c r="CJ1" s="176" t="n"/>
-      <c r="CK1" s="176" t="n"/>
-      <c r="CL1" s="176" t="n"/>
-      <c r="CM1" s="176" t="n"/>
-      <c r="CN1" s="176" t="n"/>
-      <c r="CO1" s="176" t="n"/>
-      <c r="CP1" s="176" t="n"/>
-      <c r="CQ1" s="176" t="n"/>
-      <c r="CR1" s="176" t="n"/>
-      <c r="CS1" s="177" t="n"/>
+      <c r="BP1" s="361" t="n"/>
+      <c r="BQ1" s="361" t="n"/>
+      <c r="BR1" s="361" t="n"/>
+      <c r="BS1" s="361" t="n"/>
+      <c r="BT1" s="361" t="n"/>
+      <c r="BU1" s="361" t="n"/>
+      <c r="BV1" s="361" t="n"/>
+      <c r="BW1" s="361" t="n"/>
+      <c r="BX1" s="361" t="n"/>
+      <c r="BY1" s="361" t="n"/>
+      <c r="BZ1" s="361" t="n"/>
+      <c r="CA1" s="361" t="n"/>
+      <c r="CB1" s="361" t="n"/>
+      <c r="CC1" s="361" t="n"/>
+      <c r="CD1" s="361" t="n"/>
+      <c r="CE1" s="361" t="n"/>
+      <c r="CF1" s="361" t="n"/>
+      <c r="CG1" s="361" t="n"/>
+      <c r="CH1" s="361" t="n"/>
+      <c r="CI1" s="361" t="n"/>
+      <c r="CJ1" s="361" t="n"/>
+      <c r="CK1" s="361" t="n"/>
+      <c r="CL1" s="361" t="n"/>
+      <c r="CM1" s="361" t="n"/>
+      <c r="CN1" s="361" t="n"/>
+      <c r="CO1" s="361" t="n"/>
+      <c r="CP1" s="361" t="n"/>
+      <c r="CQ1" s="361" t="n"/>
+      <c r="CR1" s="361" t="n"/>
+      <c r="CS1" s="362" t="n"/>
       <c r="CT1" s="414" t="inlineStr">
         <is>
           <t>9월</t>
         </is>
       </c>
-      <c r="CU1" s="176" t="n"/>
-      <c r="CV1" s="176" t="n"/>
-      <c r="CW1" s="176" t="n"/>
-      <c r="CX1" s="176" t="n"/>
-      <c r="CY1" s="176" t="n"/>
-      <c r="CZ1" s="176" t="n"/>
-      <c r="DA1" s="176" t="n"/>
-      <c r="DB1" s="176" t="n"/>
-      <c r="DC1" s="176" t="n"/>
-      <c r="DD1" s="176" t="n"/>
-      <c r="DE1" s="176" t="n"/>
-      <c r="DF1" s="176" t="n"/>
-      <c r="DG1" s="176" t="n"/>
-      <c r="DH1" s="176" t="n"/>
-      <c r="DI1" s="176" t="n"/>
-      <c r="DJ1" s="176" t="n"/>
-      <c r="DK1" s="176" t="n"/>
-      <c r="DL1" s="176" t="n"/>
-      <c r="DM1" s="176" t="n"/>
-      <c r="DN1" s="176" t="n"/>
-      <c r="DO1" s="176" t="n"/>
-      <c r="DP1" s="176" t="n"/>
-      <c r="DQ1" s="176" t="n"/>
-      <c r="DR1" s="176" t="n"/>
-      <c r="DS1" s="176" t="n"/>
-      <c r="DT1" s="176" t="n"/>
-      <c r="DU1" s="176" t="n"/>
-      <c r="DV1" s="176" t="n"/>
-      <c r="DW1" s="177" t="n"/>
+      <c r="CU1" s="361" t="n"/>
+      <c r="CV1" s="361" t="n"/>
+      <c r="CW1" s="361" t="n"/>
+      <c r="CX1" s="361" t="n"/>
+      <c r="CY1" s="361" t="n"/>
+      <c r="CZ1" s="361" t="n"/>
+      <c r="DA1" s="361" t="n"/>
+      <c r="DB1" s="361" t="n"/>
+      <c r="DC1" s="361" t="n"/>
+      <c r="DD1" s="361" t="n"/>
+      <c r="DE1" s="361" t="n"/>
+      <c r="DF1" s="361" t="n"/>
+      <c r="DG1" s="361" t="n"/>
+      <c r="DH1" s="361" t="n"/>
+      <c r="DI1" s="361" t="n"/>
+      <c r="DJ1" s="361" t="n"/>
+      <c r="DK1" s="361" t="n"/>
+      <c r="DL1" s="361" t="n"/>
+      <c r="DM1" s="361" t="n"/>
+      <c r="DN1" s="361" t="n"/>
+      <c r="DO1" s="361" t="n"/>
+      <c r="DP1" s="361" t="n"/>
+      <c r="DQ1" s="361" t="n"/>
+      <c r="DR1" s="361" t="n"/>
+      <c r="DS1" s="361" t="n"/>
+      <c r="DT1" s="361" t="n"/>
+      <c r="DU1" s="361" t="n"/>
+      <c r="DV1" s="361" t="n"/>
+      <c r="DW1" s="362" t="n"/>
       <c r="DX1" s="414" t="inlineStr">
         <is>
           <t>10월</t>
         </is>
       </c>
-      <c r="DY1" s="176" t="n"/>
-      <c r="DZ1" s="176" t="n"/>
-      <c r="EA1" s="176" t="n"/>
-      <c r="EB1" s="176" t="n"/>
-      <c r="EC1" s="176" t="n"/>
-      <c r="ED1" s="176" t="n"/>
-      <c r="EE1" s="176" t="n"/>
-      <c r="EF1" s="176" t="n"/>
-      <c r="EG1" s="176" t="n"/>
-      <c r="EH1" s="176" t="n"/>
-      <c r="EI1" s="176" t="n"/>
-      <c r="EJ1" s="176" t="n"/>
-      <c r="EK1" s="176" t="n"/>
-      <c r="EL1" s="176" t="n"/>
-      <c r="EM1" s="176" t="n"/>
-      <c r="EN1" s="176" t="n"/>
-      <c r="EO1" s="176" t="n"/>
-      <c r="EP1" s="176" t="n"/>
-      <c r="EQ1" s="176" t="n"/>
-      <c r="ER1" s="176" t="n"/>
-      <c r="ES1" s="176" t="n"/>
-      <c r="ET1" s="176" t="n"/>
-      <c r="EU1" s="176" t="n"/>
-      <c r="EV1" s="176" t="n"/>
-      <c r="EW1" s="176" t="n"/>
-      <c r="EX1" s="176" t="n"/>
-      <c r="EY1" s="176" t="n"/>
-      <c r="EZ1" s="176" t="n"/>
-      <c r="FA1" s="176" t="n"/>
-      <c r="FB1" s="177" t="n"/>
+      <c r="DY1" s="361" t="n"/>
+      <c r="DZ1" s="361" t="n"/>
+      <c r="EA1" s="361" t="n"/>
+      <c r="EB1" s="361" t="n"/>
+      <c r="EC1" s="361" t="n"/>
+      <c r="ED1" s="361" t="n"/>
+      <c r="EE1" s="361" t="n"/>
+      <c r="EF1" s="361" t="n"/>
+      <c r="EG1" s="361" t="n"/>
+      <c r="EH1" s="361" t="n"/>
+      <c r="EI1" s="361" t="n"/>
+      <c r="EJ1" s="361" t="n"/>
+      <c r="EK1" s="361" t="n"/>
+      <c r="EL1" s="361" t="n"/>
+      <c r="EM1" s="361" t="n"/>
+      <c r="EN1" s="361" t="n"/>
+      <c r="EO1" s="361" t="n"/>
+      <c r="EP1" s="361" t="n"/>
+      <c r="EQ1" s="361" t="n"/>
+      <c r="ER1" s="361" t="n"/>
+      <c r="ES1" s="361" t="n"/>
+      <c r="ET1" s="361" t="n"/>
+      <c r="EU1" s="361" t="n"/>
+      <c r="EV1" s="361" t="n"/>
+      <c r="EW1" s="361" t="n"/>
+      <c r="EX1" s="361" t="n"/>
+      <c r="EY1" s="361" t="n"/>
+      <c r="EZ1" s="361" t="n"/>
+      <c r="FA1" s="361" t="n"/>
+      <c r="FB1" s="362" t="n"/>
       <c r="FC1" s="414" t="inlineStr">
         <is>
           <t>11월</t>
         </is>
       </c>
-      <c r="FD1" s="176" t="n"/>
-      <c r="FE1" s="176" t="n"/>
-      <c r="FF1" s="176" t="n"/>
-      <c r="FG1" s="176" t="n"/>
-      <c r="FH1" s="176" t="n"/>
-      <c r="FI1" s="176" t="n"/>
-      <c r="FJ1" s="176" t="n"/>
-      <c r="FK1" s="176" t="n"/>
-      <c r="FL1" s="176" t="n"/>
-      <c r="FM1" s="176" t="n"/>
-      <c r="FN1" s="176" t="n"/>
-      <c r="FO1" s="176" t="n"/>
-      <c r="FP1" s="176" t="n"/>
-      <c r="FQ1" s="176" t="n"/>
-      <c r="FR1" s="176" t="n"/>
-      <c r="FS1" s="176" t="n"/>
-      <c r="FT1" s="176" t="n"/>
-      <c r="FU1" s="176" t="n"/>
-      <c r="FV1" s="176" t="n"/>
-      <c r="FW1" s="176" t="n"/>
-      <c r="FX1" s="176" t="n"/>
-      <c r="FY1" s="176" t="n"/>
-      <c r="FZ1" s="176" t="n"/>
-      <c r="GA1" s="176" t="n"/>
-      <c r="GB1" s="176" t="n"/>
-      <c r="GC1" s="176" t="n"/>
-      <c r="GD1" s="176" t="n"/>
-      <c r="GE1" s="176" t="n"/>
-      <c r="GF1" s="177" t="n"/>
+      <c r="FD1" s="361" t="n"/>
+      <c r="FE1" s="361" t="n"/>
+      <c r="FF1" s="361" t="n"/>
+      <c r="FG1" s="361" t="n"/>
+      <c r="FH1" s="361" t="n"/>
+      <c r="FI1" s="361" t="n"/>
+      <c r="FJ1" s="361" t="n"/>
+      <c r="FK1" s="361" t="n"/>
+      <c r="FL1" s="361" t="n"/>
+      <c r="FM1" s="361" t="n"/>
+      <c r="FN1" s="361" t="n"/>
+      <c r="FO1" s="361" t="n"/>
+      <c r="FP1" s="361" t="n"/>
+      <c r="FQ1" s="361" t="n"/>
+      <c r="FR1" s="361" t="n"/>
+      <c r="FS1" s="361" t="n"/>
+      <c r="FT1" s="361" t="n"/>
+      <c r="FU1" s="361" t="n"/>
+      <c r="FV1" s="361" t="n"/>
+      <c r="FW1" s="361" t="n"/>
+      <c r="FX1" s="361" t="n"/>
+      <c r="FY1" s="361" t="n"/>
+      <c r="FZ1" s="361" t="n"/>
+      <c r="GA1" s="361" t="n"/>
+      <c r="GB1" s="361" t="n"/>
+      <c r="GC1" s="361" t="n"/>
+      <c r="GD1" s="361" t="n"/>
+      <c r="GE1" s="361" t="n"/>
+      <c r="GF1" s="362" t="n"/>
       <c r="GG1" s="414" t="inlineStr">
         <is>
           <t>12월</t>
         </is>
       </c>
-      <c r="GH1" s="176" t="n"/>
-      <c r="GI1" s="176" t="n"/>
-      <c r="GJ1" s="176" t="n"/>
-      <c r="GK1" s="176" t="n"/>
-      <c r="GL1" s="176" t="n"/>
-      <c r="GM1" s="176" t="n"/>
-      <c r="GN1" s="176" t="n"/>
-      <c r="GO1" s="176" t="n"/>
-      <c r="GP1" s="176" t="n"/>
-      <c r="GQ1" s="176" t="n"/>
-      <c r="GR1" s="176" t="n"/>
-      <c r="GS1" s="176" t="n"/>
-      <c r="GT1" s="176" t="n"/>
-      <c r="GU1" s="176" t="n"/>
-      <c r="GV1" s="176" t="n"/>
-      <c r="GW1" s="176" t="n"/>
-      <c r="GX1" s="176" t="n"/>
-      <c r="GY1" s="176" t="n"/>
-      <c r="GZ1" s="176" t="n"/>
-      <c r="HA1" s="176" t="n"/>
-      <c r="HB1" s="176" t="n"/>
-      <c r="HC1" s="176" t="n"/>
-      <c r="HD1" s="176" t="n"/>
-      <c r="HE1" s="176" t="n"/>
-      <c r="HF1" s="176" t="n"/>
-      <c r="HG1" s="176" t="n"/>
-      <c r="HH1" s="176" t="n"/>
-      <c r="HI1" s="176" t="n"/>
-      <c r="HJ1" s="176" t="n"/>
-      <c r="HK1" s="177" t="n"/>
+      <c r="GH1" s="361" t="n"/>
+      <c r="GI1" s="361" t="n"/>
+      <c r="GJ1" s="361" t="n"/>
+      <c r="GK1" s="361" t="n"/>
+      <c r="GL1" s="361" t="n"/>
+      <c r="GM1" s="361" t="n"/>
+      <c r="GN1" s="361" t="n"/>
+      <c r="GO1" s="361" t="n"/>
+      <c r="GP1" s="361" t="n"/>
+      <c r="GQ1" s="361" t="n"/>
+      <c r="GR1" s="361" t="n"/>
+      <c r="GS1" s="361" t="n"/>
+      <c r="GT1" s="361" t="n"/>
+      <c r="GU1" s="361" t="n"/>
+      <c r="GV1" s="361" t="n"/>
+      <c r="GW1" s="361" t="n"/>
+      <c r="GX1" s="361" t="n"/>
+      <c r="GY1" s="361" t="n"/>
+      <c r="GZ1" s="361" t="n"/>
+      <c r="HA1" s="361" t="n"/>
+      <c r="HB1" s="361" t="n"/>
+      <c r="HC1" s="361" t="n"/>
+      <c r="HD1" s="361" t="n"/>
+      <c r="HE1" s="361" t="n"/>
+      <c r="HF1" s="361" t="n"/>
+      <c r="HG1" s="361" t="n"/>
+      <c r="HH1" s="361" t="n"/>
+      <c r="HI1" s="361" t="n"/>
+      <c r="HJ1" s="361" t="n"/>
+      <c r="HK1" s="362" t="n"/>
       <c r="HL1" s="414" t="inlineStr">
         <is>
           <t>1월</t>
         </is>
       </c>
-      <c r="HM1" s="176" t="n"/>
-      <c r="HN1" s="176" t="n"/>
-      <c r="HO1" s="177" t="n"/>
+      <c r="HM1" s="361" t="n"/>
+      <c r="HN1" s="361" t="n"/>
+      <c r="HO1" s="362" t="n"/>
     </row>
     <row r="2" ht="15.75" customHeight="1" s="173">
       <c r="A2" s="357" t="n"/>
-      <c r="B2" s="178" t="n"/>
+      <c r="B2" s="363" t="n"/>
+      <c r="C2" s="364" t="n"/>
+      <c r="D2" s="364" t="n"/>
+      <c r="E2" s="364" t="n"/>
+      <c r="F2" s="364" t="n"/>
       <c r="G2" s="414" t="inlineStr">
         <is>
           <t>1 주차</t>
         </is>
       </c>
-      <c r="H2" s="176" t="n"/>
-      <c r="I2" s="176" t="n"/>
-      <c r="J2" s="176" t="n"/>
-      <c r="K2" s="176" t="n"/>
-      <c r="L2" s="177" t="n"/>
+      <c r="H2" s="361" t="n"/>
+      <c r="I2" s="361" t="n"/>
+      <c r="J2" s="361" t="n"/>
+      <c r="K2" s="361" t="n"/>
+      <c r="L2" s="362" t="n"/>
       <c r="M2" s="414" t="inlineStr">
         <is>
           <t>2 주차</t>
         </is>
       </c>
-      <c r="N2" s="176" t="n"/>
-      <c r="O2" s="176" t="n"/>
-      <c r="P2" s="176" t="n"/>
-      <c r="Q2" s="176" t="n"/>
-      <c r="R2" s="176" t="n"/>
-      <c r="S2" s="177" t="n"/>
+      <c r="N2" s="361" t="n"/>
+      <c r="O2" s="361" t="n"/>
+      <c r="P2" s="361" t="n"/>
+      <c r="Q2" s="361" t="n"/>
+      <c r="R2" s="361" t="n"/>
+      <c r="S2" s="362" t="n"/>
       <c r="T2" s="414" t="inlineStr">
         <is>
           <t>3 주차</t>
         </is>
       </c>
-      <c r="U2" s="176" t="n"/>
-      <c r="V2" s="176" t="n"/>
-      <c r="W2" s="176" t="n"/>
-      <c r="X2" s="176" t="n"/>
-      <c r="Y2" s="176" t="n"/>
-      <c r="Z2" s="177" t="n"/>
+      <c r="U2" s="361" t="n"/>
+      <c r="V2" s="361" t="n"/>
+      <c r="W2" s="361" t="n"/>
+      <c r="X2" s="361" t="n"/>
+      <c r="Y2" s="361" t="n"/>
+      <c r="Z2" s="362" t="n"/>
       <c r="AA2" s="414" t="inlineStr">
         <is>
           <t>4 주차</t>
         </is>
       </c>
-      <c r="AB2" s="176" t="n"/>
-      <c r="AC2" s="176" t="n"/>
-      <c r="AD2" s="176" t="n"/>
-      <c r="AE2" s="176" t="n"/>
-      <c r="AF2" s="176" t="n"/>
-      <c r="AG2" s="177" t="n"/>
+      <c r="AB2" s="361" t="n"/>
+      <c r="AC2" s="361" t="n"/>
+      <c r="AD2" s="361" t="n"/>
+      <c r="AE2" s="361" t="n"/>
+      <c r="AF2" s="361" t="n"/>
+      <c r="AG2" s="362" t="n"/>
       <c r="AH2" s="414" t="inlineStr">
         <is>
           <t>1 주차</t>
         </is>
       </c>
-      <c r="AI2" s="176" t="n"/>
-      <c r="AJ2" s="176" t="n"/>
-      <c r="AK2" s="176" t="n"/>
-      <c r="AL2" s="176" t="n"/>
-      <c r="AM2" s="176" t="n"/>
-      <c r="AN2" s="177" t="n"/>
+      <c r="AI2" s="361" t="n"/>
+      <c r="AJ2" s="361" t="n"/>
+      <c r="AK2" s="361" t="n"/>
+      <c r="AL2" s="361" t="n"/>
+      <c r="AM2" s="361" t="n"/>
+      <c r="AN2" s="362" t="n"/>
       <c r="AO2" s="414" t="inlineStr">
         <is>
           <t>2 주차</t>
         </is>
       </c>
-      <c r="AP2" s="176" t="n"/>
-      <c r="AQ2" s="176" t="n"/>
-      <c r="AR2" s="176" t="n"/>
-      <c r="AS2" s="176" t="n"/>
-      <c r="AT2" s="176" t="n"/>
-      <c r="AU2" s="177" t="n"/>
+      <c r="AP2" s="361" t="n"/>
+      <c r="AQ2" s="361" t="n"/>
+      <c r="AR2" s="361" t="n"/>
+      <c r="AS2" s="361" t="n"/>
+      <c r="AT2" s="361" t="n"/>
+      <c r="AU2" s="362" t="n"/>
       <c r="AV2" s="414" t="inlineStr">
         <is>
           <t>3 주차</t>
         </is>
       </c>
-      <c r="AW2" s="176" t="n"/>
-      <c r="AX2" s="176" t="n"/>
-      <c r="AY2" s="176" t="n"/>
-      <c r="AZ2" s="176" t="n"/>
-      <c r="BA2" s="176" t="n"/>
-      <c r="BB2" s="177" t="n"/>
+      <c r="AW2" s="361" t="n"/>
+      <c r="AX2" s="361" t="n"/>
+      <c r="AY2" s="361" t="n"/>
+      <c r="AZ2" s="361" t="n"/>
+      <c r="BA2" s="361" t="n"/>
+      <c r="BB2" s="362" t="n"/>
       <c r="BC2" s="414" t="inlineStr">
         <is>
           <t>4 주차</t>
         </is>
       </c>
-      <c r="BD2" s="176" t="n"/>
-      <c r="BE2" s="176" t="n"/>
-      <c r="BF2" s="176" t="n"/>
-      <c r="BG2" s="176" t="n"/>
-      <c r="BH2" s="176" t="n"/>
-      <c r="BI2" s="177" t="n"/>
+      <c r="BD2" s="361" t="n"/>
+      <c r="BE2" s="361" t="n"/>
+      <c r="BF2" s="361" t="n"/>
+      <c r="BG2" s="361" t="n"/>
+      <c r="BH2" s="361" t="n"/>
+      <c r="BI2" s="362" t="n"/>
       <c r="BJ2" s="414" t="inlineStr">
         <is>
           <t>5 주차</t>
         </is>
       </c>
-      <c r="BK2" s="176" t="n"/>
-      <c r="BL2" s="176" t="n"/>
-      <c r="BM2" s="176" t="n"/>
-      <c r="BN2" s="176" t="n"/>
-      <c r="BO2" s="176" t="n"/>
-      <c r="BP2" s="177" t="n"/>
+      <c r="BK2" s="361" t="n"/>
+      <c r="BL2" s="361" t="n"/>
+      <c r="BM2" s="361" t="n"/>
+      <c r="BN2" s="361" t="n"/>
+      <c r="BO2" s="361" t="n"/>
+      <c r="BP2" s="362" t="n"/>
       <c r="BQ2" s="414" t="inlineStr">
         <is>
           <t>1 주차</t>
         </is>
       </c>
-      <c r="BR2" s="176" t="n"/>
-      <c r="BS2" s="176" t="n"/>
-      <c r="BT2" s="176" t="n"/>
-      <c r="BU2" s="176" t="n"/>
-      <c r="BV2" s="176" t="n"/>
-      <c r="BW2" s="177" t="n"/>
+      <c r="BR2" s="361" t="n"/>
+      <c r="BS2" s="361" t="n"/>
+      <c r="BT2" s="361" t="n"/>
+      <c r="BU2" s="361" t="n"/>
+      <c r="BV2" s="361" t="n"/>
+      <c r="BW2" s="362" t="n"/>
       <c r="BX2" s="414" t="inlineStr">
         <is>
           <t>2 주차</t>
         </is>
       </c>
-      <c r="BY2" s="176" t="n"/>
-      <c r="BZ2" s="176" t="n"/>
-      <c r="CA2" s="176" t="n"/>
-      <c r="CB2" s="176" t="n"/>
-      <c r="CC2" s="176" t="n"/>
-      <c r="CD2" s="177" t="n"/>
+      <c r="BY2" s="361" t="n"/>
+      <c r="BZ2" s="361" t="n"/>
+      <c r="CA2" s="361" t="n"/>
+      <c r="CB2" s="361" t="n"/>
+      <c r="CC2" s="361" t="n"/>
+      <c r="CD2" s="362" t="n"/>
       <c r="CE2" s="414" t="inlineStr">
         <is>
           <t>3 주차</t>
         </is>
       </c>
-      <c r="CF2" s="176" t="n"/>
-      <c r="CG2" s="176" t="n"/>
-      <c r="CH2" s="176" t="n"/>
-      <c r="CI2" s="176" t="n"/>
-      <c r="CJ2" s="176" t="n"/>
-      <c r="CK2" s="177" t="n"/>
+      <c r="CF2" s="361" t="n"/>
+      <c r="CG2" s="361" t="n"/>
+      <c r="CH2" s="361" t="n"/>
+      <c r="CI2" s="361" t="n"/>
+      <c r="CJ2" s="361" t="n"/>
+      <c r="CK2" s="362" t="n"/>
       <c r="CL2" s="414" t="inlineStr">
         <is>
           <t>4 주차</t>
         </is>
       </c>
-      <c r="CM2" s="176" t="n"/>
-      <c r="CN2" s="176" t="n"/>
-      <c r="CO2" s="176" t="n"/>
-      <c r="CP2" s="176" t="n"/>
-      <c r="CQ2" s="176" t="n"/>
-      <c r="CR2" s="177" t="n"/>
+      <c r="CM2" s="361" t="n"/>
+      <c r="CN2" s="361" t="n"/>
+      <c r="CO2" s="361" t="n"/>
+      <c r="CP2" s="361" t="n"/>
+      <c r="CQ2" s="361" t="n"/>
+      <c r="CR2" s="362" t="n"/>
       <c r="CS2" s="414" t="inlineStr">
         <is>
           <t>1 주차</t>
         </is>
       </c>
-      <c r="CT2" s="176" t="n"/>
-      <c r="CU2" s="176" t="n"/>
-      <c r="CV2" s="176" t="n"/>
-      <c r="CW2" s="176" t="n"/>
-      <c r="CX2" s="176" t="n"/>
-      <c r="CY2" s="177" t="n"/>
+      <c r="CT2" s="361" t="n"/>
+      <c r="CU2" s="361" t="n"/>
+      <c r="CV2" s="361" t="n"/>
+      <c r="CW2" s="361" t="n"/>
+      <c r="CX2" s="361" t="n"/>
+      <c r="CY2" s="362" t="n"/>
       <c r="CZ2" s="414" t="inlineStr">
         <is>
           <t>2 주차</t>
         </is>
       </c>
-      <c r="DA2" s="176" t="n"/>
-      <c r="DB2" s="176" t="n"/>
-      <c r="DC2" s="176" t="n"/>
-      <c r="DD2" s="176" t="n"/>
-      <c r="DE2" s="176" t="n"/>
-      <c r="DF2" s="177" t="n"/>
+      <c r="DA2" s="361" t="n"/>
+      <c r="DB2" s="361" t="n"/>
+      <c r="DC2" s="361" t="n"/>
+      <c r="DD2" s="361" t="n"/>
+      <c r="DE2" s="361" t="n"/>
+      <c r="DF2" s="362" t="n"/>
       <c r="DG2" s="414" t="inlineStr">
         <is>
           <t>3 주차</t>
         </is>
       </c>
-      <c r="DH2" s="176" t="n"/>
-      <c r="DI2" s="176" t="n"/>
-      <c r="DJ2" s="176" t="n"/>
-      <c r="DK2" s="176" t="n"/>
-      <c r="DL2" s="176" t="n"/>
-      <c r="DM2" s="177" t="n"/>
+      <c r="DH2" s="361" t="n"/>
+      <c r="DI2" s="361" t="n"/>
+      <c r="DJ2" s="361" t="n"/>
+      <c r="DK2" s="361" t="n"/>
+      <c r="DL2" s="361" t="n"/>
+      <c r="DM2" s="362" t="n"/>
       <c r="DN2" s="414" t="inlineStr">
         <is>
           <t>4 주차</t>
         </is>
       </c>
-      <c r="DO2" s="176" t="n"/>
-      <c r="DP2" s="176" t="n"/>
-      <c r="DQ2" s="176" t="n"/>
-      <c r="DR2" s="176" t="n"/>
-      <c r="DS2" s="176" t="n"/>
-      <c r="DT2" s="177" t="n"/>
+      <c r="DO2" s="361" t="n"/>
+      <c r="DP2" s="361" t="n"/>
+      <c r="DQ2" s="361" t="n"/>
+      <c r="DR2" s="361" t="n"/>
+      <c r="DS2" s="361" t="n"/>
+      <c r="DT2" s="362" t="n"/>
       <c r="DU2" s="414" t="inlineStr">
         <is>
           <t>1 주차</t>
         </is>
       </c>
-      <c r="DV2" s="176" t="n"/>
-      <c r="DW2" s="176" t="n"/>
-      <c r="DX2" s="176" t="n"/>
-      <c r="DY2" s="176" t="n"/>
-      <c r="DZ2" s="176" t="n"/>
-      <c r="EA2" s="177" t="n"/>
+      <c r="DV2" s="361" t="n"/>
+      <c r="DW2" s="361" t="n"/>
+      <c r="DX2" s="361" t="n"/>
+      <c r="DY2" s="361" t="n"/>
+      <c r="DZ2" s="361" t="n"/>
+      <c r="EA2" s="362" t="n"/>
       <c r="EB2" s="414" t="inlineStr">
         <is>
           <t>2 주차</t>
         </is>
       </c>
-      <c r="EC2" s="176" t="n"/>
-      <c r="ED2" s="176" t="n"/>
-      <c r="EE2" s="176" t="n"/>
-      <c r="EF2" s="176" t="n"/>
-      <c r="EG2" s="176" t="n"/>
-      <c r="EH2" s="177" t="n"/>
+      <c r="EC2" s="361" t="n"/>
+      <c r="ED2" s="361" t="n"/>
+      <c r="EE2" s="361" t="n"/>
+      <c r="EF2" s="361" t="n"/>
+      <c r="EG2" s="361" t="n"/>
+      <c r="EH2" s="362" t="n"/>
       <c r="EI2" s="414" t="inlineStr">
         <is>
           <t>3 주차</t>
         </is>
       </c>
-      <c r="EJ2" s="176" t="n"/>
-      <c r="EK2" s="176" t="n"/>
-      <c r="EL2" s="176" t="n"/>
-      <c r="EM2" s="176" t="n"/>
-      <c r="EN2" s="176" t="n"/>
-      <c r="EO2" s="177" t="n"/>
+      <c r="EJ2" s="361" t="n"/>
+      <c r="EK2" s="361" t="n"/>
+      <c r="EL2" s="361" t="n"/>
+      <c r="EM2" s="361" t="n"/>
+      <c r="EN2" s="361" t="n"/>
+      <c r="EO2" s="362" t="n"/>
       <c r="EP2" s="414" t="inlineStr">
         <is>
           <t>4 주차</t>
         </is>
       </c>
-      <c r="EQ2" s="176" t="n"/>
-      <c r="ER2" s="176" t="n"/>
-      <c r="ES2" s="176" t="n"/>
-      <c r="ET2" s="176" t="n"/>
-      <c r="EU2" s="176" t="n"/>
-      <c r="EV2" s="177" t="n"/>
+      <c r="EQ2" s="361" t="n"/>
+      <c r="ER2" s="361" t="n"/>
+      <c r="ES2" s="361" t="n"/>
+      <c r="ET2" s="361" t="n"/>
+      <c r="EU2" s="361" t="n"/>
+      <c r="EV2" s="362" t="n"/>
       <c r="EW2" s="414" t="inlineStr">
         <is>
           <t>5 주차</t>
         </is>
       </c>
-      <c r="EX2" s="176" t="n"/>
-      <c r="EY2" s="176" t="n"/>
-      <c r="EZ2" s="176" t="n"/>
-      <c r="FA2" s="176" t="n"/>
-      <c r="FB2" s="176" t="n"/>
-      <c r="FC2" s="177" t="n"/>
+      <c r="EX2" s="361" t="n"/>
+      <c r="EY2" s="361" t="n"/>
+      <c r="EZ2" s="361" t="n"/>
+      <c r="FA2" s="361" t="n"/>
+      <c r="FB2" s="361" t="n"/>
+      <c r="FC2" s="362" t="n"/>
       <c r="FD2" s="414" t="inlineStr">
         <is>
           <t>1 주차</t>
         </is>
       </c>
-      <c r="FE2" s="176" t="n"/>
-      <c r="FF2" s="176" t="n"/>
-      <c r="FG2" s="176" t="n"/>
-      <c r="FH2" s="176" t="n"/>
-      <c r="FI2" s="176" t="n"/>
-      <c r="FJ2" s="177" t="n"/>
+      <c r="FE2" s="361" t="n"/>
+      <c r="FF2" s="361" t="n"/>
+      <c r="FG2" s="361" t="n"/>
+      <c r="FH2" s="361" t="n"/>
+      <c r="FI2" s="361" t="n"/>
+      <c r="FJ2" s="362" t="n"/>
       <c r="FK2" s="414" t="inlineStr">
         <is>
           <t>2 주차</t>
         </is>
       </c>
-      <c r="FL2" s="176" t="n"/>
-      <c r="FM2" s="176" t="n"/>
-      <c r="FN2" s="176" t="n"/>
-      <c r="FO2" s="176" t="n"/>
-      <c r="FP2" s="176" t="n"/>
-      <c r="FQ2" s="177" t="n"/>
+      <c r="FL2" s="361" t="n"/>
+      <c r="FM2" s="361" t="n"/>
+      <c r="FN2" s="361" t="n"/>
+      <c r="FO2" s="361" t="n"/>
+      <c r="FP2" s="361" t="n"/>
+      <c r="FQ2" s="362" t="n"/>
       <c r="FR2" s="414" t="inlineStr">
         <is>
           <t>3 주차</t>
         </is>
       </c>
-      <c r="FS2" s="176" t="n"/>
-      <c r="FT2" s="176" t="n"/>
-      <c r="FU2" s="176" t="n"/>
-      <c r="FV2" s="176" t="n"/>
-      <c r="FW2" s="176" t="n"/>
-      <c r="FX2" s="177" t="n"/>
+      <c r="FS2" s="361" t="n"/>
+      <c r="FT2" s="361" t="n"/>
+      <c r="FU2" s="361" t="n"/>
+      <c r="FV2" s="361" t="n"/>
+      <c r="FW2" s="361" t="n"/>
+      <c r="FX2" s="362" t="n"/>
       <c r="FY2" s="414" t="inlineStr">
         <is>
           <t>4 주차</t>
         </is>
       </c>
-      <c r="FZ2" s="176" t="n"/>
-      <c r="GA2" s="176" t="n"/>
-      <c r="GB2" s="176" t="n"/>
-      <c r="GC2" s="176" t="n"/>
-      <c r="GD2" s="176" t="n"/>
-      <c r="GE2" s="177" t="n"/>
+      <c r="FZ2" s="361" t="n"/>
+      <c r="GA2" s="361" t="n"/>
+      <c r="GB2" s="361" t="n"/>
+      <c r="GC2" s="361" t="n"/>
+      <c r="GD2" s="361" t="n"/>
+      <c r="GE2" s="362" t="n"/>
       <c r="GF2" s="414" t="inlineStr">
         <is>
           <t>1 주차</t>
         </is>
       </c>
-      <c r="GG2" s="176" t="n"/>
-      <c r="GH2" s="176" t="n"/>
-      <c r="GI2" s="176" t="n"/>
-      <c r="GJ2" s="176" t="n"/>
-      <c r="GK2" s="176" t="n"/>
-      <c r="GL2" s="177" t="n"/>
+      <c r="GG2" s="361" t="n"/>
+      <c r="GH2" s="361" t="n"/>
+      <c r="GI2" s="361" t="n"/>
+      <c r="GJ2" s="361" t="n"/>
+      <c r="GK2" s="361" t="n"/>
+      <c r="GL2" s="362" t="n"/>
       <c r="GM2" s="414" t="inlineStr">
         <is>
           <t>2 주차</t>
         </is>
       </c>
-      <c r="GN2" s="176" t="n"/>
-      <c r="GO2" s="176" t="n"/>
-      <c r="GP2" s="176" t="n"/>
-      <c r="GQ2" s="176" t="n"/>
-      <c r="GR2" s="176" t="n"/>
-      <c r="GS2" s="177" t="n"/>
+      <c r="GN2" s="361" t="n"/>
+      <c r="GO2" s="361" t="n"/>
+      <c r="GP2" s="361" t="n"/>
+      <c r="GQ2" s="361" t="n"/>
+      <c r="GR2" s="361" t="n"/>
+      <c r="GS2" s="362" t="n"/>
       <c r="GT2" s="414" t="inlineStr">
         <is>
           <t>3 주차</t>
         </is>
       </c>
-      <c r="GU2" s="176" t="n"/>
-      <c r="GV2" s="176" t="n"/>
-      <c r="GW2" s="176" t="n"/>
-      <c r="GX2" s="176" t="n"/>
-      <c r="GY2" s="176" t="n"/>
-      <c r="GZ2" s="177" t="n"/>
+      <c r="GU2" s="361" t="n"/>
+      <c r="GV2" s="361" t="n"/>
+      <c r="GW2" s="361" t="n"/>
+      <c r="GX2" s="361" t="n"/>
+      <c r="GY2" s="361" t="n"/>
+      <c r="GZ2" s="362" t="n"/>
       <c r="HA2" s="414" t="inlineStr">
         <is>
           <t>4 주차</t>
         </is>
       </c>
-      <c r="HB2" s="176" t="n"/>
-      <c r="HC2" s="176" t="n"/>
-      <c r="HD2" s="176" t="n"/>
-      <c r="HE2" s="176" t="n"/>
-      <c r="HF2" s="176" t="n"/>
-      <c r="HG2" s="177" t="n"/>
+      <c r="HB2" s="361" t="n"/>
+      <c r="HC2" s="361" t="n"/>
+      <c r="HD2" s="361" t="n"/>
+      <c r="HE2" s="361" t="n"/>
+      <c r="HF2" s="361" t="n"/>
+      <c r="HG2" s="362" t="n"/>
       <c r="HH2" s="414" t="inlineStr">
         <is>
           <t>5 주차</t>
         </is>
       </c>
-      <c r="HI2" s="176" t="n"/>
-      <c r="HJ2" s="176" t="n"/>
-      <c r="HK2" s="176" t="n"/>
-      <c r="HL2" s="176" t="n"/>
-      <c r="HM2" s="176" t="n"/>
-      <c r="HN2" s="177" t="n"/>
+      <c r="HI2" s="361" t="n"/>
+      <c r="HJ2" s="361" t="n"/>
+      <c r="HK2" s="361" t="n"/>
+      <c r="HL2" s="361" t="n"/>
+      <c r="HM2" s="361" t="n"/>
+      <c r="HN2" s="362" t="n"/>
       <c r="HO2" s="414" t="inlineStr">
         <is>
           <t>1 주차</t>
@@ -3172,7 +3176,11 @@
     </row>
     <row r="3" ht="15.75" customHeight="1" s="173">
       <c r="A3" s="357" t="n"/>
-      <c r="B3" s="178" t="n"/>
+      <c r="B3" s="363" t="n"/>
+      <c r="C3" s="364" t="n"/>
+      <c r="D3" s="364" t="n"/>
+      <c r="E3" s="364" t="n"/>
+      <c r="F3" s="364" t="n"/>
       <c r="G3" s="366" t="n">
         <v>2</v>
       </c>
@@ -10650,7 +10658,7 @@
       <c r="E29" s="416" t="n"/>
       <c r="F29" s="417" t="inlineStr">
         <is>
-          <t>7월 4~5주차</t>
+          <t>1차 완료</t>
         </is>
       </c>
       <c r="G29" s="376" t="n"/>
@@ -10701,18 +10709,18 @@
       <c r="AZ29" s="375" t="n"/>
       <c r="BA29" s="375" t="n"/>
       <c r="BB29" s="375" t="n"/>
-      <c r="BC29" s="396" t="n"/>
-      <c r="BD29" s="396" t="n"/>
-      <c r="BE29" s="396" t="n"/>
-      <c r="BF29" s="396" t="n"/>
-      <c r="BG29" s="396" t="n"/>
+      <c r="BC29" s="374" t="n"/>
+      <c r="BD29" s="374" t="n"/>
+      <c r="BE29" s="374" t="n"/>
+      <c r="BF29" s="374" t="n"/>
+      <c r="BG29" s="374" t="n"/>
       <c r="BH29" s="375" t="n"/>
       <c r="BI29" s="375" t="n"/>
-      <c r="BJ29" s="396" t="n"/>
-      <c r="BK29" s="396" t="n"/>
-      <c r="BL29" s="396" t="n"/>
-      <c r="BM29" s="396" t="n"/>
-      <c r="BN29" s="396" t="n"/>
+      <c r="BJ29" s="374" t="n"/>
+      <c r="BK29" s="374" t="n"/>
+      <c r="BL29" s="374" t="n"/>
+      <c r="BM29" s="374" t="n"/>
+      <c r="BN29" s="374" t="n"/>
       <c r="BO29" s="375" t="n"/>
       <c r="BP29" s="375" t="n"/>
       <c r="BQ29" s="376" t="n"/>
@@ -10887,7 +10895,7 @@
       <c r="E30" s="418" t="n"/>
       <c r="F30" s="419" t="inlineStr">
         <is>
-          <t>7월 4~5주차</t>
+          <t>1차 완료</t>
         </is>
       </c>
       <c r="G30" s="376" t="n"/>
@@ -10938,18 +10946,18 @@
       <c r="AZ30" s="375" t="n"/>
       <c r="BA30" s="375" t="n"/>
       <c r="BB30" s="375" t="n"/>
-      <c r="BC30" s="396" t="n"/>
-      <c r="BD30" s="396" t="n"/>
-      <c r="BE30" s="396" t="n"/>
-      <c r="BF30" s="396" t="n"/>
-      <c r="BG30" s="396" t="n"/>
+      <c r="BC30" s="374" t="n"/>
+      <c r="BD30" s="374" t="n"/>
+      <c r="BE30" s="374" t="n"/>
+      <c r="BF30" s="374" t="n"/>
+      <c r="BG30" s="374" t="n"/>
       <c r="BH30" s="375" t="n"/>
       <c r="BI30" s="375" t="n"/>
-      <c r="BJ30" s="396" t="n"/>
-      <c r="BK30" s="396" t="n"/>
-      <c r="BL30" s="396" t="n"/>
-      <c r="BM30" s="396" t="n"/>
-      <c r="BN30" s="396" t="n"/>
+      <c r="BJ30" s="374" t="n"/>
+      <c r="BK30" s="374" t="n"/>
+      <c r="BL30" s="374" t="n"/>
+      <c r="BM30" s="374" t="n"/>
+      <c r="BN30" s="374" t="n"/>
       <c r="BO30" s="375" t="n"/>
       <c r="BP30" s="375" t="n"/>
       <c r="BQ30" s="376" t="n"/>
@@ -11124,7 +11132,7 @@
       <c r="E31" s="418" t="n"/>
       <c r="F31" s="419" t="inlineStr">
         <is>
-          <t>7월 4~5주차</t>
+          <t>1차 완료</t>
         </is>
       </c>
       <c r="G31" s="376" t="n"/>
@@ -11175,18 +11183,18 @@
       <c r="AZ31" s="375" t="n"/>
       <c r="BA31" s="375" t="n"/>
       <c r="BB31" s="375" t="n"/>
-      <c r="BC31" s="396" t="n"/>
-      <c r="BD31" s="396" t="n"/>
-      <c r="BE31" s="396" t="n"/>
-      <c r="BF31" s="396" t="n"/>
-      <c r="BG31" s="396" t="n"/>
+      <c r="BC31" s="374" t="n"/>
+      <c r="BD31" s="374" t="n"/>
+      <c r="BE31" s="374" t="n"/>
+      <c r="BF31" s="374" t="n"/>
+      <c r="BG31" s="374" t="n"/>
       <c r="BH31" s="375" t="n"/>
       <c r="BI31" s="375" t="n"/>
-      <c r="BJ31" s="396" t="n"/>
-      <c r="BK31" s="396" t="n"/>
-      <c r="BL31" s="396" t="n"/>
-      <c r="BM31" s="396" t="n"/>
-      <c r="BN31" s="396" t="n"/>
+      <c r="BJ31" s="374" t="n"/>
+      <c r="BK31" s="374" t="n"/>
+      <c r="BL31" s="374" t="n"/>
+      <c r="BM31" s="374" t="n"/>
+      <c r="BN31" s="374" t="n"/>
       <c r="BO31" s="375" t="n"/>
       <c r="BP31" s="375" t="n"/>
       <c r="BQ31" s="376" t="n"/>
@@ -11361,7 +11369,7 @@
       <c r="E32" s="418" t="n"/>
       <c r="F32" s="419" t="inlineStr">
         <is>
-          <t>7월 4~5주차</t>
+          <t>1차 완료</t>
         </is>
       </c>
       <c r="G32" s="376" t="n"/>
@@ -11412,18 +11420,18 @@
       <c r="AZ32" s="375" t="n"/>
       <c r="BA32" s="375" t="n"/>
       <c r="BB32" s="375" t="n"/>
-      <c r="BC32" s="396" t="n"/>
-      <c r="BD32" s="396" t="n"/>
-      <c r="BE32" s="396" t="n"/>
-      <c r="BF32" s="396" t="n"/>
-      <c r="BG32" s="396" t="n"/>
+      <c r="BC32" s="374" t="n"/>
+      <c r="BD32" s="374" t="n"/>
+      <c r="BE32" s="374" t="n"/>
+      <c r="BF32" s="374" t="n"/>
+      <c r="BG32" s="374" t="n"/>
       <c r="BH32" s="375" t="n"/>
       <c r="BI32" s="375" t="n"/>
-      <c r="BJ32" s="396" t="n"/>
-      <c r="BK32" s="396" t="n"/>
-      <c r="BL32" s="396" t="n"/>
-      <c r="BM32" s="396" t="n"/>
-      <c r="BN32" s="396" t="n"/>
+      <c r="BJ32" s="374" t="n"/>
+      <c r="BK32" s="374" t="n"/>
+      <c r="BL32" s="374" t="n"/>
+      <c r="BM32" s="374" t="n"/>
+      <c r="BN32" s="374" t="n"/>
       <c r="BO32" s="375" t="n"/>
       <c r="BP32" s="375" t="n"/>
       <c r="BQ32" s="376" t="n"/>
@@ -11598,7 +11606,7 @@
       <c r="E33" s="418" t="n"/>
       <c r="F33" s="419" t="inlineStr">
         <is>
-          <t>7월 4~5주차</t>
+          <t>1차 완료</t>
         </is>
       </c>
       <c r="G33" s="376" t="n"/>
@@ -11649,18 +11657,18 @@
       <c r="AZ33" s="375" t="n"/>
       <c r="BA33" s="375" t="n"/>
       <c r="BB33" s="375" t="n"/>
-      <c r="BC33" s="396" t="n"/>
-      <c r="BD33" s="396" t="n"/>
-      <c r="BE33" s="396" t="n"/>
-      <c r="BF33" s="396" t="n"/>
-      <c r="BG33" s="396" t="n"/>
+      <c r="BC33" s="374" t="n"/>
+      <c r="BD33" s="374" t="n"/>
+      <c r="BE33" s="374" t="n"/>
+      <c r="BF33" s="374" t="n"/>
+      <c r="BG33" s="374" t="n"/>
       <c r="BH33" s="375" t="n"/>
       <c r="BI33" s="375" t="n"/>
-      <c r="BJ33" s="396" t="n"/>
-      <c r="BK33" s="396" t="n"/>
-      <c r="BL33" s="396" t="n"/>
-      <c r="BM33" s="396" t="n"/>
-      <c r="BN33" s="396" t="n"/>
+      <c r="BJ33" s="374" t="n"/>
+      <c r="BK33" s="374" t="n"/>
+      <c r="BL33" s="374" t="n"/>
+      <c r="BM33" s="374" t="n"/>
+      <c r="BN33" s="374" t="n"/>
       <c r="BO33" s="375" t="n"/>
       <c r="BP33" s="375" t="n"/>
       <c r="BQ33" s="376" t="n"/>
@@ -11839,7 +11847,7 @@
       </c>
       <c r="F34" s="423" t="inlineStr">
         <is>
-          <t>7월 4~5주차</t>
+          <t>1차 완료</t>
         </is>
       </c>
       <c r="G34" s="376" t="n"/>
@@ -11890,18 +11898,18 @@
       <c r="AZ34" s="375" t="n"/>
       <c r="BA34" s="375" t="n"/>
       <c r="BB34" s="375" t="n"/>
-      <c r="BC34" s="396" t="n"/>
-      <c r="BD34" s="396" t="n"/>
-      <c r="BE34" s="396" t="n"/>
-      <c r="BF34" s="396" t="n"/>
-      <c r="BG34" s="396" t="n"/>
+      <c r="BC34" s="374" t="n"/>
+      <c r="BD34" s="374" t="n"/>
+      <c r="BE34" s="374" t="n"/>
+      <c r="BF34" s="374" t="n"/>
+      <c r="BG34" s="374" t="n"/>
       <c r="BH34" s="375" t="n"/>
       <c r="BI34" s="375" t="n"/>
-      <c r="BJ34" s="396" t="n"/>
-      <c r="BK34" s="396" t="n"/>
-      <c r="BL34" s="396" t="n"/>
-      <c r="BM34" s="396" t="n"/>
-      <c r="BN34" s="396" t="n"/>
+      <c r="BJ34" s="374" t="n"/>
+      <c r="BK34" s="374" t="n"/>
+      <c r="BL34" s="374" t="n"/>
+      <c r="BM34" s="374" t="n"/>
+      <c r="BN34" s="374" t="n"/>
       <c r="BO34" s="375" t="n"/>
       <c r="BP34" s="375" t="n"/>
       <c r="BQ34" s="376" t="n"/>
@@ -14706,6 +14714,10 @@
           <t>■ 범례</t>
         </is>
       </c>
+      <c r="C46" s="364" t="n"/>
+      <c r="D46" s="364" t="n"/>
+      <c r="E46" s="364" t="n"/>
+      <c r="F46" s="364" t="n"/>
       <c r="G46" s="172" t="n"/>
       <c r="H46" s="172" t="n"/>
       <c r="I46" s="172" t="n"/>
@@ -14932,6 +14944,9 @@
           <t>완료 (작업 완료 · 1차 완료)</t>
         </is>
       </c>
+      <c r="D47" s="364" t="n"/>
+      <c r="E47" s="364" t="n"/>
+      <c r="F47" s="364" t="n"/>
       <c r="G47" s="172" t="n"/>
       <c r="H47" s="172" t="n"/>
       <c r="I47" s="172" t="n"/>
@@ -15158,6 +15173,9 @@
           <t>마일스톤 / 기준선</t>
         </is>
       </c>
+      <c r="D48" s="364" t="n"/>
+      <c r="E48" s="364" t="n"/>
+      <c r="F48" s="364" t="n"/>
       <c r="G48" s="172" t="n"/>
       <c r="H48" s="172" t="n"/>
       <c r="I48" s="172" t="n"/>
@@ -15384,6 +15402,9 @@
           <t>예정 — 데이터 검수 · 최종 검증 · 완료 보고</t>
         </is>
       </c>
+      <c r="D49" s="364" t="n"/>
+      <c r="E49" s="364" t="n"/>
+      <c r="F49" s="364" t="n"/>
       <c r="G49" s="172" t="n"/>
       <c r="H49" s="172" t="n"/>
       <c r="I49" s="172" t="n"/>
@@ -15610,6 +15631,9 @@
           <t>예정 — 배포 준비 · 시스템 연계</t>
         </is>
       </c>
+      <c r="D50" s="364" t="n"/>
+      <c r="E50" s="364" t="n"/>
+      <c r="F50" s="364" t="n"/>
       <c r="G50" s="172" t="n"/>
       <c r="H50" s="172" t="n"/>
       <c r="I50" s="172" t="n"/>
@@ -15836,6 +15860,9 @@
           <t>예정 — KL API 협의 · 베타 · 감리</t>
         </is>
       </c>
+      <c r="D51" s="364" t="n"/>
+      <c r="E51" s="364" t="n"/>
+      <c r="F51" s="364" t="n"/>
       <c r="G51" s="172" t="n"/>
       <c r="H51" s="172" t="n"/>
       <c r="I51" s="172" t="n"/>
@@ -51204,7 +51231,6 @@
     <mergeCell ref="BQ2:BW2"/>
     <mergeCell ref="DG2:DM2"/>
     <mergeCell ref="DU2:EA2"/>
-    <mergeCell ref="B28:E28"/>
     <mergeCell ref="GF2:GL2"/>
     <mergeCell ref="FC1:GF1"/>
     <mergeCell ref="B46:F46"/>
@@ -51218,8 +51244,9 @@
     <mergeCell ref="DN2:DT2"/>
     <mergeCell ref="C49:F49"/>
     <mergeCell ref="AJ1:BN1"/>
+    <mergeCell ref="G1:AI1"/>
+    <mergeCell ref="C19:C21"/>
     <mergeCell ref="EB2:EH2"/>
-    <mergeCell ref="C19:C21"/>
     <mergeCell ref="GM2:GS2"/>
     <mergeCell ref="AO2:AU2"/>
     <mergeCell ref="C24:C26"/>
@@ -51239,12 +51266,13 @@
     <mergeCell ref="C50:F50"/>
     <mergeCell ref="AV2:BB2"/>
     <mergeCell ref="DX1:FB1"/>
+    <mergeCell ref="BJ2:BP2"/>
     <mergeCell ref="B5:B8"/>
-    <mergeCell ref="BJ2:BP2"/>
     <mergeCell ref="B9:B16"/>
     <mergeCell ref="CZ2:DF2"/>
     <mergeCell ref="G2:L2"/>
     <mergeCell ref="EI2:EO2"/>
+    <mergeCell ref="HL1:HO1"/>
     <mergeCell ref="GT2:GZ2"/>
     <mergeCell ref="CS2:CY2"/>
     <mergeCell ref="FD2:FJ2"/>
@@ -51253,10 +51281,9 @@
     <mergeCell ref="FR2:FX2"/>
     <mergeCell ref="C5:C6"/>
     <mergeCell ref="C51:F51"/>
+    <mergeCell ref="HH2:HN2"/>
     <mergeCell ref="T2:Z2"/>
-    <mergeCell ref="HH2:HN2"/>
-    <mergeCell ref="G1:AI1"/>
-    <mergeCell ref="HL1:HO1"/>
+    <mergeCell ref="B28:E28"/>
     <mergeCell ref="CT1:DW1"/>
   </mergeCells>
   <dataValidations count="1">

--- a/doc/result/감리정본/[지재원] AI 영업비밀관리시스템 구축 WBS.xlsx
+++ b/doc/result/감리정본/[지재원] AI 영업비밀관리시스템 구축 WBS.xlsx
@@ -1020,7 +1020,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="430">
+  <cellXfs count="432">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -2057,6 +2057,8 @@
     <xf numFmtId="0" fontId="30" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2332,7 +2334,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:HO236"/>
+  <dimension ref="A1:HO240"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" style="173" min="1" max="1"/>
@@ -14482,424 +14484,440 @@
       <c r="HN44" s="375" t="n"/>
       <c r="HO44" s="376" t="n"/>
     </row>
-    <row r="45" ht="15.75" customHeight="1" s="173">
-      <c r="A45" s="156" t="n"/>
-      <c r="B45" s="156" t="n"/>
-      <c r="C45" s="156" t="n"/>
-      <c r="D45" s="171" t="n"/>
-      <c r="E45" s="171" t="n"/>
-      <c r="F45" s="156" t="n"/>
-      <c r="G45" s="172" t="n"/>
-      <c r="H45" s="172" t="n"/>
-      <c r="I45" s="172" t="n"/>
-      <c r="J45" s="172" t="n"/>
-      <c r="K45" s="172" t="n"/>
-      <c r="L45" s="172" t="n"/>
-      <c r="M45" s="172" t="n"/>
-      <c r="N45" s="172" t="n"/>
-      <c r="O45" s="172" t="n"/>
-      <c r="P45" s="172" t="n"/>
-      <c r="Q45" s="172" t="n"/>
-      <c r="R45" s="172" t="n"/>
-      <c r="S45" s="172" t="n"/>
-      <c r="T45" s="172" t="n"/>
-      <c r="U45" s="172" t="n"/>
-      <c r="V45" s="172" t="n"/>
-      <c r="W45" s="172" t="n"/>
-      <c r="X45" s="172" t="n"/>
-      <c r="Y45" s="172" t="n"/>
-      <c r="Z45" s="172" t="n"/>
-      <c r="AA45" s="172" t="n"/>
-      <c r="AB45" s="172" t="n"/>
-      <c r="AC45" s="172" t="n"/>
-      <c r="AD45" s="172" t="n"/>
-      <c r="AE45" s="172" t="n"/>
-      <c r="AF45" s="172" t="n"/>
-      <c r="AG45" s="172" t="n"/>
-      <c r="AH45" s="172" t="n"/>
-      <c r="AI45" s="172" t="n"/>
-      <c r="AJ45" s="172" t="n"/>
-      <c r="AK45" s="172" t="n"/>
-      <c r="AL45" s="172" t="n"/>
-      <c r="AM45" s="172" t="n"/>
-      <c r="AN45" s="172" t="n"/>
-      <c r="AO45" s="172" t="n"/>
-      <c r="AP45" s="172" t="n"/>
-      <c r="AQ45" s="172" t="n"/>
-      <c r="AR45" s="172" t="n"/>
-      <c r="AS45" s="172" t="n"/>
-      <c r="AT45" s="172" t="n"/>
-      <c r="AU45" s="172" t="n"/>
-      <c r="AV45" s="172" t="n"/>
-      <c r="AW45" s="172" t="n"/>
-      <c r="AX45" s="172" t="n"/>
-      <c r="AY45" s="172" t="n"/>
-      <c r="AZ45" s="172" t="n"/>
-      <c r="BA45" s="172" t="n"/>
-      <c r="BB45" s="172" t="n"/>
-      <c r="BC45" s="172" t="n"/>
-      <c r="BD45" s="172" t="n"/>
-      <c r="BE45" s="172" t="n"/>
-      <c r="BF45" s="172" t="n"/>
-      <c r="BG45" s="172" t="n"/>
-      <c r="BH45" s="172" t="n"/>
-      <c r="BI45" s="172" t="n"/>
-      <c r="BJ45" s="172" t="n"/>
-      <c r="BK45" s="172" t="n"/>
-      <c r="BL45" s="172" t="n"/>
-      <c r="BM45" s="172" t="n"/>
-      <c r="BN45" s="172" t="n"/>
-      <c r="BO45" s="172" t="n"/>
-      <c r="BP45" s="172" t="n"/>
-      <c r="BQ45" s="172" t="n"/>
-      <c r="BR45" s="172" t="n"/>
-      <c r="BS45" s="172" t="n"/>
-      <c r="BT45" s="172" t="n"/>
-      <c r="BU45" s="172" t="n"/>
-      <c r="BV45" s="172" t="n"/>
-      <c r="BW45" s="172" t="n"/>
-      <c r="BX45" s="172" t="n"/>
-      <c r="BY45" s="172" t="n"/>
-      <c r="BZ45" s="172" t="n"/>
-      <c r="CA45" s="172" t="n"/>
-      <c r="CB45" s="172" t="n"/>
-      <c r="CC45" s="172" t="n"/>
-      <c r="CD45" s="172" t="n"/>
-      <c r="CE45" s="172" t="n"/>
-      <c r="CF45" s="172" t="n"/>
-      <c r="CG45" s="172" t="n"/>
-      <c r="CH45" s="172" t="n"/>
-      <c r="CI45" s="172" t="n"/>
-      <c r="CJ45" s="172" t="n"/>
-      <c r="CK45" s="172" t="n"/>
-      <c r="CL45" s="172" t="n"/>
-      <c r="CM45" s="172" t="n"/>
-      <c r="CN45" s="172" t="n"/>
-      <c r="CO45" s="172" t="n"/>
-      <c r="CP45" s="172" t="n"/>
-      <c r="CQ45" s="172" t="n"/>
-      <c r="CR45" s="172" t="n"/>
-      <c r="CS45" s="172" t="n"/>
-      <c r="CT45" s="172" t="n"/>
-      <c r="CU45" s="172" t="n"/>
-      <c r="CV45" s="172" t="n"/>
-      <c r="CW45" s="172" t="n"/>
-      <c r="CX45" s="172" t="n"/>
-      <c r="CY45" s="172" t="n"/>
-      <c r="CZ45" s="172" t="n"/>
-      <c r="DA45" s="172" t="n"/>
-      <c r="DB45" s="172" t="n"/>
-      <c r="DC45" s="172" t="n"/>
-      <c r="DD45" s="172" t="n"/>
-      <c r="DE45" s="172" t="n"/>
-      <c r="DF45" s="172" t="n"/>
-      <c r="DG45" s="172" t="n"/>
-      <c r="DH45" s="172" t="n"/>
-      <c r="DI45" s="172" t="n"/>
-      <c r="DJ45" s="172" t="n"/>
-      <c r="DK45" s="172" t="n"/>
-      <c r="DL45" s="172" t="n"/>
-      <c r="DM45" s="172" t="n"/>
-      <c r="DN45" s="172" t="n"/>
-      <c r="DO45" s="172" t="n"/>
-      <c r="DP45" s="172" t="n"/>
-      <c r="DQ45" s="172" t="n"/>
-      <c r="DR45" s="172" t="n"/>
-      <c r="DS45" s="172" t="n"/>
-      <c r="DT45" s="172" t="n"/>
-      <c r="DU45" s="172" t="n"/>
-      <c r="DV45" s="172" t="n"/>
-      <c r="DW45" s="172" t="n"/>
-      <c r="DX45" s="172" t="n"/>
-      <c r="DY45" s="172" t="n"/>
-      <c r="DZ45" s="172" t="n"/>
-      <c r="EA45" s="172" t="n"/>
-      <c r="EB45" s="172" t="n"/>
-      <c r="EC45" s="172" t="n"/>
-      <c r="ED45" s="172" t="n"/>
-      <c r="EE45" s="172" t="n"/>
-      <c r="EF45" s="172" t="n"/>
-      <c r="EG45" s="172" t="n"/>
-      <c r="EH45" s="172" t="n"/>
-      <c r="EI45" s="172" t="n"/>
-      <c r="EJ45" s="172" t="n"/>
-      <c r="EK45" s="172" t="n"/>
-      <c r="EL45" s="172" t="n"/>
-      <c r="EM45" s="172" t="n"/>
-      <c r="EN45" s="172" t="n"/>
-      <c r="EO45" s="172" t="n"/>
-      <c r="EP45" s="172" t="n"/>
-      <c r="EQ45" s="172" t="n"/>
-      <c r="ER45" s="172" t="n"/>
-      <c r="ES45" s="172" t="n"/>
-      <c r="ET45" s="172" t="n"/>
-      <c r="EU45" s="172" t="n"/>
-      <c r="EV45" s="172" t="n"/>
-      <c r="EW45" s="172" t="n"/>
-      <c r="EX45" s="172" t="n"/>
-      <c r="EY45" s="172" t="n"/>
-      <c r="EZ45" s="172" t="n"/>
-      <c r="FA45" s="172" t="n"/>
-      <c r="FB45" s="172" t="n"/>
-      <c r="FC45" s="172" t="n"/>
-      <c r="FD45" s="172" t="n"/>
-      <c r="FE45" s="172" t="n"/>
-      <c r="FF45" s="172" t="n"/>
-      <c r="FG45" s="172" t="n"/>
-      <c r="FH45" s="172" t="n"/>
-      <c r="FI45" s="172" t="n"/>
-      <c r="FJ45" s="172" t="n"/>
-      <c r="FK45" s="172" t="n"/>
-      <c r="FL45" s="172" t="n"/>
-      <c r="FM45" s="172" t="n"/>
-      <c r="FN45" s="172" t="n"/>
-      <c r="FO45" s="172" t="n"/>
-      <c r="FP45" s="172" t="n"/>
-      <c r="FQ45" s="172" t="n"/>
-      <c r="FR45" s="172" t="n"/>
-      <c r="FS45" s="172" t="n"/>
-      <c r="FT45" s="172" t="n"/>
-      <c r="FU45" s="172" t="n"/>
-      <c r="FV45" s="172" t="n"/>
-      <c r="FW45" s="172" t="n"/>
-      <c r="FX45" s="172" t="n"/>
-      <c r="FY45" s="172" t="n"/>
-      <c r="FZ45" s="172" t="n"/>
-      <c r="GA45" s="172" t="n"/>
-      <c r="GB45" s="172" t="n"/>
-      <c r="GC45" s="172" t="n"/>
-      <c r="GD45" s="172" t="n"/>
-      <c r="GE45" s="172" t="n"/>
-      <c r="GF45" s="172" t="n"/>
+    <row r="45" ht="32" customHeight="1" s="173">
+      <c r="A45" s="364" t="n"/>
+      <c r="B45" s="425" t="inlineStr">
+        <is>
+          <t>제3자 감리</t>
+        </is>
+      </c>
+      <c r="C45" s="424" t="inlineStr">
+        <is>
+          <t>사전 진단</t>
+        </is>
+      </c>
+      <c r="D45" s="425" t="inlineStr">
+        <is>
+          <t>요구사항정의서·산출물 목록·작성 수준·사업관리 체계 점검 대응</t>
+        </is>
+      </c>
+      <c r="E45" s="425" t="inlineStr">
+        <is>
+          <t>제출 산출물 동결본</t>
+        </is>
+      </c>
+      <c r="F45" s="426" t="inlineStr">
+        <is>
+          <t>8월 2주차</t>
+        </is>
+      </c>
+      <c r="G45" s="364" t="n"/>
+      <c r="H45" s="364" t="n"/>
+      <c r="I45" s="364" t="n"/>
+      <c r="J45" s="364" t="n"/>
+      <c r="K45" s="430" t="n"/>
+      <c r="L45" s="430" t="n"/>
+      <c r="M45" s="364" t="n"/>
+      <c r="N45" s="364" t="n"/>
+      <c r="O45" s="364" t="n"/>
+      <c r="P45" s="364" t="n"/>
+      <c r="Q45" s="364" t="n"/>
+      <c r="R45" s="430" t="n"/>
+      <c r="S45" s="430" t="n"/>
+      <c r="T45" s="364" t="n"/>
+      <c r="U45" s="364" t="n"/>
+      <c r="V45" s="364" t="n"/>
+      <c r="W45" s="364" t="n"/>
+      <c r="X45" s="364" t="n"/>
+      <c r="Y45" s="430" t="n"/>
+      <c r="Z45" s="430" t="n"/>
+      <c r="AA45" s="364" t="n"/>
+      <c r="AB45" s="364" t="n"/>
+      <c r="AC45" s="364" t="n"/>
+      <c r="AD45" s="364" t="n"/>
+      <c r="AE45" s="364" t="n"/>
+      <c r="AF45" s="430" t="n"/>
+      <c r="AG45" s="430" t="n"/>
+      <c r="AH45" s="364" t="n"/>
+      <c r="AI45" s="364" t="n"/>
+      <c r="AJ45" s="364" t="n"/>
+      <c r="AK45" s="364" t="n"/>
+      <c r="AL45" s="364" t="n"/>
+      <c r="AM45" s="430" t="n"/>
+      <c r="AN45" s="430" t="n"/>
+      <c r="AO45" s="364" t="n"/>
+      <c r="AP45" s="364" t="n"/>
+      <c r="AQ45" s="364" t="n"/>
+      <c r="AR45" s="364" t="n"/>
+      <c r="AS45" s="364" t="n"/>
+      <c r="AT45" s="430" t="n"/>
+      <c r="AU45" s="430" t="n"/>
+      <c r="AV45" s="364" t="n"/>
+      <c r="AW45" s="364" t="n"/>
+      <c r="AX45" s="364" t="n"/>
+      <c r="AY45" s="364" t="n"/>
+      <c r="AZ45" s="430" t="n"/>
+      <c r="BA45" s="430" t="n"/>
+      <c r="BB45" s="430" t="n"/>
+      <c r="BC45" s="364" t="n"/>
+      <c r="BD45" s="364" t="n"/>
+      <c r="BE45" s="364" t="n"/>
+      <c r="BF45" s="364" t="n"/>
+      <c r="BG45" s="364" t="n"/>
+      <c r="BH45" s="430" t="n"/>
+      <c r="BI45" s="430" t="n"/>
+      <c r="BJ45" s="364" t="n"/>
+      <c r="BK45" s="364" t="n"/>
+      <c r="BL45" s="364" t="n"/>
+      <c r="BM45" s="364" t="n"/>
+      <c r="BN45" s="364" t="n"/>
+      <c r="BO45" s="430" t="n"/>
+      <c r="BP45" s="430" t="n"/>
+      <c r="BQ45" s="364" t="n"/>
+      <c r="BR45" s="364" t="n"/>
+      <c r="BS45" s="364" t="n"/>
+      <c r="BT45" s="364" t="n"/>
+      <c r="BU45" s="364" t="n"/>
+      <c r="BV45" s="430" t="n"/>
+      <c r="BW45" s="430" t="n"/>
+      <c r="BX45" s="431" t="n"/>
+      <c r="BY45" s="431" t="n"/>
+      <c r="BZ45" s="431" t="n"/>
+      <c r="CA45" s="431" t="n"/>
+      <c r="CB45" s="431" t="n"/>
+      <c r="CC45" s="430" t="n"/>
+      <c r="CD45" s="430" t="n"/>
+      <c r="CE45" s="430" t="n"/>
+      <c r="CF45" s="364" t="n"/>
+      <c r="CG45" s="364" t="n"/>
+      <c r="CH45" s="364" t="n"/>
+      <c r="CI45" s="364" t="n"/>
+      <c r="CJ45" s="430" t="n"/>
+      <c r="CK45" s="430" t="n"/>
+      <c r="CL45" s="364" t="n"/>
+      <c r="CM45" s="364" t="n"/>
+      <c r="CN45" s="364" t="n"/>
+      <c r="CO45" s="364" t="n"/>
+      <c r="CP45" s="364" t="n"/>
+      <c r="CQ45" s="430" t="n"/>
+      <c r="CR45" s="430" t="n"/>
+      <c r="CS45" s="364" t="n"/>
+      <c r="CT45" s="364" t="n"/>
+      <c r="CU45" s="364" t="n"/>
+      <c r="CV45" s="364" t="n"/>
+      <c r="CW45" s="364" t="n"/>
+      <c r="CX45" s="430" t="n"/>
+      <c r="CY45" s="430" t="n"/>
+      <c r="CZ45" s="364" t="n"/>
+      <c r="DA45" s="364" t="n"/>
+      <c r="DB45" s="364" t="n"/>
+      <c r="DC45" s="364" t="n"/>
+      <c r="DD45" s="364" t="n"/>
+      <c r="DE45" s="430" t="n"/>
+      <c r="DF45" s="430" t="n"/>
+      <c r="DG45" s="364" t="n"/>
+      <c r="DH45" s="364" t="n"/>
+      <c r="DI45" s="364" t="n"/>
+      <c r="DJ45" s="364" t="n"/>
+      <c r="DK45" s="364" t="n"/>
+      <c r="DL45" s="430" t="n"/>
+      <c r="DM45" s="430" t="n"/>
+      <c r="DN45" s="364" t="n"/>
+      <c r="DO45" s="364" t="n"/>
+      <c r="DP45" s="364" t="n"/>
+      <c r="DQ45" s="430" t="n"/>
+      <c r="DR45" s="430" t="n"/>
+      <c r="DS45" s="430" t="n"/>
+      <c r="DT45" s="430" t="n"/>
+      <c r="DU45" s="364" t="n"/>
+      <c r="DV45" s="364" t="n"/>
+      <c r="DW45" s="364" t="n"/>
+      <c r="DX45" s="364" t="n"/>
+      <c r="DY45" s="364" t="n"/>
+      <c r="DZ45" s="430" t="n"/>
+      <c r="EA45" s="430" t="n"/>
+      <c r="EB45" s="430" t="n"/>
+      <c r="EC45" s="364" t="n"/>
+      <c r="ED45" s="364" t="n"/>
+      <c r="EE45" s="364" t="n"/>
+      <c r="EF45" s="430" t="n"/>
+      <c r="EG45" s="430" t="n"/>
+      <c r="EH45" s="430" t="n"/>
+      <c r="EI45" s="364" t="n"/>
+      <c r="EJ45" s="364" t="n"/>
+      <c r="EK45" s="364" t="n"/>
+      <c r="EL45" s="364" t="n"/>
+      <c r="EM45" s="364" t="n"/>
+      <c r="EN45" s="430" t="n"/>
+      <c r="EO45" s="430" t="n"/>
+      <c r="EP45" s="364" t="n"/>
+      <c r="EQ45" s="364" t="n"/>
+      <c r="ER45" s="364" t="n"/>
+      <c r="ES45" s="364" t="n"/>
+      <c r="ET45" s="364" t="n"/>
+      <c r="EU45" s="430" t="n"/>
+      <c r="EV45" s="430" t="n"/>
+      <c r="EW45" s="364" t="n"/>
+      <c r="EX45" s="364" t="n"/>
+      <c r="EY45" s="364" t="n"/>
+      <c r="EZ45" s="364" t="n"/>
+      <c r="FA45" s="364" t="n"/>
+      <c r="FB45" s="430" t="n"/>
+      <c r="FC45" s="430" t="n"/>
+      <c r="FD45" s="364" t="n"/>
+      <c r="FE45" s="364" t="n"/>
+      <c r="FF45" s="364" t="n"/>
+      <c r="FG45" s="364" t="n"/>
+      <c r="FH45" s="364" t="n"/>
+      <c r="FI45" s="430" t="n"/>
+      <c r="FJ45" s="430" t="n"/>
+      <c r="FK45" s="364" t="n"/>
+      <c r="FL45" s="364" t="n"/>
+      <c r="FM45" s="364" t="n"/>
+      <c r="FN45" s="364" t="n"/>
+      <c r="FO45" s="364" t="n"/>
+      <c r="FP45" s="430" t="n"/>
+      <c r="FQ45" s="430" t="n"/>
+      <c r="FR45" s="364" t="n"/>
+      <c r="FS45" s="364" t="n"/>
+      <c r="FT45" s="364" t="n"/>
+      <c r="FU45" s="364" t="n"/>
+      <c r="FV45" s="364" t="n"/>
+      <c r="FW45" s="430" t="n"/>
+      <c r="FX45" s="430" t="n"/>
+      <c r="FY45" s="364" t="n"/>
+      <c r="FZ45" s="364" t="n"/>
+      <c r="GA45" s="364" t="n"/>
+      <c r="GB45" s="364" t="n"/>
+      <c r="GC45" s="364" t="n"/>
+      <c r="GD45" s="430" t="n"/>
+      <c r="GE45" s="430" t="n"/>
+      <c r="GF45" s="364" t="n"/>
       <c r="GG45" s="364" t="n"/>
       <c r="GH45" s="364" t="n"/>
       <c r="GI45" s="364" t="n"/>
       <c r="GJ45" s="364" t="n"/>
-      <c r="GK45" s="364" t="n"/>
-      <c r="GL45" s="364" t="n"/>
+      <c r="GK45" s="430" t="n"/>
+      <c r="GL45" s="430" t="n"/>
       <c r="GM45" s="364" t="n"/>
       <c r="GN45" s="364" t="n"/>
       <c r="GO45" s="364" t="n"/>
       <c r="GP45" s="364" t="n"/>
       <c r="GQ45" s="364" t="n"/>
-      <c r="GR45" s="364" t="n"/>
-      <c r="GS45" s="364" t="n"/>
+      <c r="GR45" s="430" t="n"/>
+      <c r="GS45" s="430" t="n"/>
       <c r="GT45" s="364" t="n"/>
       <c r="GU45" s="364" t="n"/>
       <c r="GV45" s="364" t="n"/>
       <c r="GW45" s="364" t="n"/>
       <c r="GX45" s="364" t="n"/>
-      <c r="GY45" s="364" t="n"/>
-      <c r="GZ45" s="364" t="n"/>
+      <c r="GY45" s="430" t="n"/>
+      <c r="GZ45" s="430" t="n"/>
       <c r="HA45" s="364" t="n"/>
       <c r="HB45" s="364" t="n"/>
       <c r="HC45" s="364" t="n"/>
       <c r="HD45" s="364" t="n"/>
-      <c r="HE45" s="364" t="n"/>
-      <c r="HF45" s="364" t="n"/>
-      <c r="HG45" s="364" t="n"/>
+      <c r="HE45" s="430" t="n"/>
+      <c r="HF45" s="430" t="n"/>
+      <c r="HG45" s="430" t="n"/>
       <c r="HH45" s="364" t="n"/>
       <c r="HI45" s="364" t="n"/>
       <c r="HJ45" s="364" t="n"/>
       <c r="HK45" s="364" t="n"/>
-      <c r="HL45" s="364" t="n"/>
-      <c r="HM45" s="364" t="n"/>
-      <c r="HN45" s="364" t="n"/>
+      <c r="HL45" s="430" t="n"/>
+      <c r="HM45" s="430" t="n"/>
+      <c r="HN45" s="430" t="n"/>
       <c r="HO45" s="364" t="n"/>
     </row>
-    <row r="46" ht="15.75" customHeight="1" s="173">
-      <c r="A46" s="156" t="n"/>
-      <c r="B46" s="402" t="inlineStr">
-        <is>
-          <t>■ 범례</t>
-        </is>
-      </c>
-      <c r="C46" s="364" t="n"/>
-      <c r="D46" s="364" t="n"/>
-      <c r="E46" s="364" t="n"/>
-      <c r="F46" s="364" t="n"/>
-      <c r="G46" s="172" t="n"/>
-      <c r="H46" s="172" t="n"/>
-      <c r="I46" s="172" t="n"/>
-      <c r="J46" s="172" t="n"/>
-      <c r="K46" s="172" t="n"/>
-      <c r="L46" s="172" t="n"/>
-      <c r="M46" s="172" t="n"/>
-      <c r="N46" s="172" t="n"/>
-      <c r="O46" s="172" t="n"/>
-      <c r="P46" s="172" t="n"/>
-      <c r="Q46" s="172" t="n"/>
-      <c r="R46" s="172" t="n"/>
-      <c r="S46" s="172" t="n"/>
-      <c r="T46" s="172" t="n"/>
-      <c r="U46" s="172" t="n"/>
-      <c r="V46" s="172" t="n"/>
-      <c r="W46" s="172" t="n"/>
-      <c r="X46" s="172" t="n"/>
-      <c r="Y46" s="172" t="n"/>
-      <c r="Z46" s="172" t="n"/>
-      <c r="AA46" s="172" t="n"/>
-      <c r="AB46" s="172" t="n"/>
-      <c r="AC46" s="172" t="n"/>
-      <c r="AD46" s="172" t="n"/>
-      <c r="AE46" s="172" t="n"/>
-      <c r="AF46" s="172" t="n"/>
-      <c r="AG46" s="172" t="n"/>
-      <c r="AH46" s="172" t="n"/>
-      <c r="AI46" s="172" t="n"/>
-      <c r="AJ46" s="172" t="n"/>
-      <c r="AK46" s="172" t="n"/>
-      <c r="AL46" s="172" t="n"/>
-      <c r="AM46" s="172" t="n"/>
-      <c r="AN46" s="172" t="n"/>
-      <c r="AO46" s="172" t="n"/>
-      <c r="AP46" s="172" t="n"/>
-      <c r="AQ46" s="172" t="n"/>
-      <c r="AR46" s="172" t="n"/>
-      <c r="AS46" s="172" t="n"/>
-      <c r="AT46" s="172" t="n"/>
-      <c r="AU46" s="172" t="n"/>
-      <c r="AV46" s="172" t="n"/>
-      <c r="AW46" s="172" t="n"/>
-      <c r="AX46" s="172" t="n"/>
-      <c r="AY46" s="172" t="n"/>
-      <c r="AZ46" s="172" t="n"/>
-      <c r="BA46" s="172" t="n"/>
-      <c r="BB46" s="172" t="n"/>
-      <c r="BC46" s="172" t="n"/>
-      <c r="BD46" s="172" t="n"/>
-      <c r="BE46" s="172" t="n"/>
-      <c r="BF46" s="172" t="n"/>
-      <c r="BG46" s="172" t="n"/>
-      <c r="BH46" s="172" t="n"/>
-      <c r="BI46" s="172" t="n"/>
-      <c r="BJ46" s="172" t="n"/>
-      <c r="BK46" s="172" t="n"/>
-      <c r="BL46" s="172" t="n"/>
-      <c r="BM46" s="172" t="n"/>
-      <c r="BN46" s="172" t="n"/>
-      <c r="BO46" s="172" t="n"/>
-      <c r="BP46" s="172" t="n"/>
-      <c r="BQ46" s="172" t="n"/>
-      <c r="BR46" s="172" t="n"/>
-      <c r="BS46" s="172" t="n"/>
-      <c r="BT46" s="172" t="n"/>
-      <c r="BU46" s="172" t="n"/>
-      <c r="BV46" s="172" t="n"/>
-      <c r="BW46" s="172" t="n"/>
-      <c r="BX46" s="172" t="n"/>
-      <c r="BY46" s="172" t="n"/>
-      <c r="BZ46" s="172" t="n"/>
-      <c r="CA46" s="172" t="n"/>
-      <c r="CB46" s="172" t="n"/>
-      <c r="CC46" s="172" t="n"/>
-      <c r="CD46" s="172" t="n"/>
-      <c r="CE46" s="172" t="n"/>
-      <c r="CF46" s="172" t="n"/>
-      <c r="CG46" s="172" t="n"/>
-      <c r="CH46" s="172" t="n"/>
-      <c r="CI46" s="172" t="n"/>
-      <c r="CJ46" s="172" t="n"/>
-      <c r="CK46" s="172" t="n"/>
-      <c r="CL46" s="172" t="n"/>
-      <c r="CM46" s="172" t="n"/>
-      <c r="CN46" s="172" t="n"/>
-      <c r="CO46" s="172" t="n"/>
-      <c r="CP46" s="172" t="n"/>
-      <c r="CQ46" s="172" t="n"/>
-      <c r="CR46" s="172" t="n"/>
-      <c r="CS46" s="172" t="n"/>
-      <c r="CT46" s="172" t="n"/>
-      <c r="CU46" s="172" t="n"/>
-      <c r="CV46" s="172" t="n"/>
-      <c r="CW46" s="172" t="n"/>
-      <c r="CX46" s="172" t="n"/>
-      <c r="CY46" s="172" t="n"/>
-      <c r="CZ46" s="172" t="n"/>
-      <c r="DA46" s="172" t="n"/>
-      <c r="DB46" s="172" t="n"/>
-      <c r="DC46" s="172" t="n"/>
-      <c r="DD46" s="172" t="n"/>
-      <c r="DE46" s="172" t="n"/>
-      <c r="DF46" s="172" t="n"/>
-      <c r="DG46" s="172" t="n"/>
-      <c r="DH46" s="172" t="n"/>
-      <c r="DI46" s="172" t="n"/>
-      <c r="DJ46" s="172" t="n"/>
-      <c r="DK46" s="172" t="n"/>
-      <c r="DL46" s="172" t="n"/>
-      <c r="DM46" s="172" t="n"/>
-      <c r="DN46" s="172" t="n"/>
-      <c r="DO46" s="172" t="n"/>
-      <c r="DP46" s="172" t="n"/>
-      <c r="DQ46" s="172" t="n"/>
-      <c r="DR46" s="172" t="n"/>
-      <c r="DS46" s="172" t="n"/>
-      <c r="DT46" s="172" t="n"/>
-      <c r="DU46" s="172" t="n"/>
-      <c r="DV46" s="172" t="n"/>
-      <c r="DW46" s="172" t="n"/>
-      <c r="DX46" s="172" t="n"/>
-      <c r="DY46" s="172" t="n"/>
-      <c r="DZ46" s="172" t="n"/>
-      <c r="EA46" s="172" t="n"/>
-      <c r="EB46" s="172" t="n"/>
-      <c r="EC46" s="172" t="n"/>
-      <c r="ED46" s="172" t="n"/>
-      <c r="EE46" s="172" t="n"/>
-      <c r="EF46" s="172" t="n"/>
-      <c r="EG46" s="172" t="n"/>
-      <c r="EH46" s="172" t="n"/>
-      <c r="EI46" s="172" t="n"/>
-      <c r="EJ46" s="172" t="n"/>
-      <c r="EK46" s="172" t="n"/>
-      <c r="EL46" s="172" t="n"/>
-      <c r="EM46" s="172" t="n"/>
-      <c r="EN46" s="172" t="n"/>
-      <c r="EO46" s="172" t="n"/>
-      <c r="EP46" s="172" t="n"/>
-      <c r="EQ46" s="172" t="n"/>
-      <c r="ER46" s="172" t="n"/>
-      <c r="ES46" s="172" t="n"/>
-      <c r="ET46" s="172" t="n"/>
-      <c r="EU46" s="172" t="n"/>
-      <c r="EV46" s="172" t="n"/>
-      <c r="EW46" s="172" t="n"/>
-      <c r="EX46" s="172" t="n"/>
-      <c r="EY46" s="172" t="n"/>
-      <c r="EZ46" s="172" t="n"/>
-      <c r="FA46" s="172" t="n"/>
-      <c r="FB46" s="172" t="n"/>
-      <c r="FC46" s="172" t="n"/>
-      <c r="FD46" s="172" t="n"/>
-      <c r="FE46" s="172" t="n"/>
-      <c r="FF46" s="172" t="n"/>
-      <c r="FG46" s="172" t="n"/>
-      <c r="FH46" s="172" t="n"/>
-      <c r="FI46" s="172" t="n"/>
-      <c r="FJ46" s="172" t="n"/>
-      <c r="FK46" s="172" t="n"/>
-      <c r="FL46" s="172" t="n"/>
-      <c r="FM46" s="172" t="n"/>
-      <c r="FN46" s="172" t="n"/>
-      <c r="FO46" s="172" t="n"/>
-      <c r="FP46" s="172" t="n"/>
-      <c r="FQ46" s="172" t="n"/>
-      <c r="FR46" s="172" t="n"/>
-      <c r="FS46" s="172" t="n"/>
-      <c r="FT46" s="172" t="n"/>
-      <c r="FU46" s="172" t="n"/>
-      <c r="FV46" s="172" t="n"/>
-      <c r="FW46" s="172" t="n"/>
-      <c r="FX46" s="172" t="n"/>
-      <c r="FY46" s="172" t="n"/>
-      <c r="FZ46" s="172" t="n"/>
-      <c r="GA46" s="172" t="n"/>
-      <c r="GB46" s="172" t="n"/>
-      <c r="GC46" s="172" t="n"/>
-      <c r="GD46" s="172" t="n"/>
-      <c r="GE46" s="172" t="n"/>
-      <c r="GF46" s="172" t="n"/>
+    <row r="46" ht="32" customHeight="1" s="173">
+      <c r="A46" s="364" t="n"/>
+      <c r="B46" s="425" t="inlineStr"/>
+      <c r="C46" s="361" t="n"/>
+      <c r="D46" s="361" t="n"/>
+      <c r="E46" s="361" t="n"/>
+      <c r="F46" s="362" t="n"/>
+      <c r="G46" s="364" t="n"/>
+      <c r="H46" s="364" t="n"/>
+      <c r="I46" s="364" t="n"/>
+      <c r="J46" s="364" t="n"/>
+      <c r="K46" s="364" t="n"/>
+      <c r="L46" s="364" t="n"/>
+      <c r="M46" s="364" t="n"/>
+      <c r="N46" s="364" t="n"/>
+      <c r="O46" s="364" t="n"/>
+      <c r="P46" s="364" t="n"/>
+      <c r="Q46" s="364" t="n"/>
+      <c r="R46" s="364" t="n"/>
+      <c r="S46" s="364" t="n"/>
+      <c r="T46" s="364" t="n"/>
+      <c r="U46" s="364" t="n"/>
+      <c r="V46" s="364" t="n"/>
+      <c r="W46" s="364" t="n"/>
+      <c r="X46" s="364" t="n"/>
+      <c r="Y46" s="364" t="n"/>
+      <c r="Z46" s="364" t="n"/>
+      <c r="AA46" s="364" t="n"/>
+      <c r="AB46" s="364" t="n"/>
+      <c r="AC46" s="364" t="n"/>
+      <c r="AD46" s="364" t="n"/>
+      <c r="AE46" s="364" t="n"/>
+      <c r="AF46" s="364" t="n"/>
+      <c r="AG46" s="364" t="n"/>
+      <c r="AH46" s="364" t="n"/>
+      <c r="AI46" s="364" t="n"/>
+      <c r="AJ46" s="364" t="n"/>
+      <c r="AK46" s="364" t="n"/>
+      <c r="AL46" s="364" t="n"/>
+      <c r="AM46" s="364" t="n"/>
+      <c r="AN46" s="364" t="n"/>
+      <c r="AO46" s="364" t="n"/>
+      <c r="AP46" s="364" t="n"/>
+      <c r="AQ46" s="364" t="n"/>
+      <c r="AR46" s="364" t="n"/>
+      <c r="AS46" s="364" t="n"/>
+      <c r="AT46" s="364" t="n"/>
+      <c r="AU46" s="364" t="n"/>
+      <c r="AV46" s="364" t="n"/>
+      <c r="AW46" s="364" t="n"/>
+      <c r="AX46" s="364" t="n"/>
+      <c r="AY46" s="364" t="n"/>
+      <c r="AZ46" s="364" t="n"/>
+      <c r="BA46" s="364" t="n"/>
+      <c r="BB46" s="364" t="n"/>
+      <c r="BC46" s="364" t="n"/>
+      <c r="BD46" s="364" t="n"/>
+      <c r="BE46" s="364" t="n"/>
+      <c r="BF46" s="364" t="n"/>
+      <c r="BG46" s="364" t="n"/>
+      <c r="BH46" s="364" t="n"/>
+      <c r="BI46" s="364" t="n"/>
+      <c r="BJ46" s="364" t="n"/>
+      <c r="BK46" s="364" t="n"/>
+      <c r="BL46" s="364" t="n"/>
+      <c r="BM46" s="364" t="n"/>
+      <c r="BN46" s="364" t="n"/>
+      <c r="BO46" s="364" t="n"/>
+      <c r="BP46" s="364" t="n"/>
+      <c r="BQ46" s="364" t="n"/>
+      <c r="BR46" s="364" t="n"/>
+      <c r="BS46" s="364" t="n"/>
+      <c r="BT46" s="364" t="n"/>
+      <c r="BU46" s="364" t="n"/>
+      <c r="BV46" s="364" t="n"/>
+      <c r="BW46" s="364" t="n"/>
+      <c r="BX46" s="364" t="n"/>
+      <c r="BY46" s="364" t="n"/>
+      <c r="BZ46" s="364" t="n"/>
+      <c r="CA46" s="364" t="n"/>
+      <c r="CB46" s="364" t="n"/>
+      <c r="CC46" s="364" t="n"/>
+      <c r="CD46" s="364" t="n"/>
+      <c r="CE46" s="364" t="n"/>
+      <c r="CF46" s="364" t="n"/>
+      <c r="CG46" s="364" t="n"/>
+      <c r="CH46" s="364" t="n"/>
+      <c r="CI46" s="364" t="n"/>
+      <c r="CJ46" s="364" t="n"/>
+      <c r="CK46" s="364" t="n"/>
+      <c r="CL46" s="364" t="n"/>
+      <c r="CM46" s="364" t="n"/>
+      <c r="CN46" s="364" t="n"/>
+      <c r="CO46" s="364" t="n"/>
+      <c r="CP46" s="364" t="n"/>
+      <c r="CQ46" s="364" t="n"/>
+      <c r="CR46" s="364" t="n"/>
+      <c r="CS46" s="431" t="n"/>
+      <c r="CT46" s="431" t="n"/>
+      <c r="CU46" s="431" t="n"/>
+      <c r="CV46" s="431" t="n"/>
+      <c r="CW46" s="431" t="n"/>
+      <c r="CX46" s="364" t="n"/>
+      <c r="CY46" s="364" t="n"/>
+      <c r="CZ46" s="364" t="n"/>
+      <c r="DA46" s="364" t="n"/>
+      <c r="DB46" s="364" t="n"/>
+      <c r="DC46" s="364" t="n"/>
+      <c r="DD46" s="364" t="n"/>
+      <c r="DE46" s="364" t="n"/>
+      <c r="DF46" s="364" t="n"/>
+      <c r="DG46" s="364" t="n"/>
+      <c r="DH46" s="364" t="n"/>
+      <c r="DI46" s="364" t="n"/>
+      <c r="DJ46" s="364" t="n"/>
+      <c r="DK46" s="364" t="n"/>
+      <c r="DL46" s="364" t="n"/>
+      <c r="DM46" s="364" t="n"/>
+      <c r="DN46" s="364" t="n"/>
+      <c r="DO46" s="364" t="n"/>
+      <c r="DP46" s="364" t="n"/>
+      <c r="DQ46" s="364" t="n"/>
+      <c r="DR46" s="364" t="n"/>
+      <c r="DS46" s="364" t="n"/>
+      <c r="DT46" s="364" t="n"/>
+      <c r="DU46" s="364" t="n"/>
+      <c r="DV46" s="364" t="n"/>
+      <c r="DW46" s="364" t="n"/>
+      <c r="DX46" s="364" t="n"/>
+      <c r="DY46" s="364" t="n"/>
+      <c r="DZ46" s="364" t="n"/>
+      <c r="EA46" s="364" t="n"/>
+      <c r="EB46" s="364" t="n"/>
+      <c r="EC46" s="364" t="n"/>
+      <c r="ED46" s="364" t="n"/>
+      <c r="EE46" s="364" t="n"/>
+      <c r="EF46" s="364" t="n"/>
+      <c r="EG46" s="364" t="n"/>
+      <c r="EH46" s="364" t="n"/>
+      <c r="EI46" s="364" t="n"/>
+      <c r="EJ46" s="364" t="n"/>
+      <c r="EK46" s="364" t="n"/>
+      <c r="EL46" s="364" t="n"/>
+      <c r="EM46" s="364" t="n"/>
+      <c r="EN46" s="364" t="n"/>
+      <c r="EO46" s="364" t="n"/>
+      <c r="EP46" s="364" t="n"/>
+      <c r="EQ46" s="364" t="n"/>
+      <c r="ER46" s="364" t="n"/>
+      <c r="ES46" s="364" t="n"/>
+      <c r="ET46" s="364" t="n"/>
+      <c r="EU46" s="364" t="n"/>
+      <c r="EV46" s="364" t="n"/>
+      <c r="EW46" s="364" t="n"/>
+      <c r="EX46" s="364" t="n"/>
+      <c r="EY46" s="364" t="n"/>
+      <c r="EZ46" s="364" t="n"/>
+      <c r="FA46" s="364" t="n"/>
+      <c r="FB46" s="364" t="n"/>
+      <c r="FC46" s="364" t="n"/>
+      <c r="FD46" s="364" t="n"/>
+      <c r="FE46" s="364" t="n"/>
+      <c r="FF46" s="364" t="n"/>
+      <c r="FG46" s="364" t="n"/>
+      <c r="FH46" s="364" t="n"/>
+      <c r="FI46" s="364" t="n"/>
+      <c r="FJ46" s="364" t="n"/>
+      <c r="FK46" s="364" t="n"/>
+      <c r="FL46" s="364" t="n"/>
+      <c r="FM46" s="364" t="n"/>
+      <c r="FN46" s="364" t="n"/>
+      <c r="FO46" s="364" t="n"/>
+      <c r="FP46" s="364" t="n"/>
+      <c r="FQ46" s="364" t="n"/>
+      <c r="FR46" s="364" t="n"/>
+      <c r="FS46" s="364" t="n"/>
+      <c r="FT46" s="364" t="n"/>
+      <c r="FU46" s="364" t="n"/>
+      <c r="FV46" s="364" t="n"/>
+      <c r="FW46" s="364" t="n"/>
+      <c r="FX46" s="364" t="n"/>
+      <c r="FY46" s="364" t="n"/>
+      <c r="FZ46" s="364" t="n"/>
+      <c r="GA46" s="364" t="n"/>
+      <c r="GB46" s="364" t="n"/>
+      <c r="GC46" s="364" t="n"/>
+      <c r="GD46" s="364" t="n"/>
+      <c r="GE46" s="364" t="n"/>
+      <c r="GF46" s="364" t="n"/>
       <c r="GG46" s="364" t="n"/>
       <c r="GH46" s="364" t="n"/>
       <c r="GI46" s="364" t="n"/>
@@ -14936,199 +14954,199 @@
       <c r="HN46" s="364" t="n"/>
       <c r="HO46" s="364" t="n"/>
     </row>
-    <row r="47" ht="15.75" customHeight="1" s="173">
-      <c r="A47" s="156" t="n"/>
-      <c r="B47" s="403" t="n"/>
-      <c r="C47" s="404" t="inlineStr">
+    <row r="47" ht="32" customHeight="1" s="173">
+      <c r="A47" s="364" t="n"/>
+      <c r="B47" s="425" t="inlineStr"/>
+      <c r="C47" s="424" t="inlineStr">
         <is>
-          <t>완료 (작업 완료 · 1차 완료)</t>
+          <t>테스트 사전점검</t>
         </is>
       </c>
-      <c r="D47" s="364" t="n"/>
-      <c r="E47" s="364" t="n"/>
-      <c r="F47" s="364" t="n"/>
-      <c r="G47" s="172" t="n"/>
-      <c r="H47" s="172" t="n"/>
-      <c r="I47" s="172" t="n"/>
-      <c r="J47" s="172" t="n"/>
-      <c r="K47" s="172" t="n"/>
-      <c r="L47" s="172" t="n"/>
-      <c r="M47" s="172" t="n"/>
-      <c r="N47" s="172" t="n"/>
-      <c r="O47" s="172" t="n"/>
-      <c r="P47" s="172" t="n"/>
-      <c r="Q47" s="172" t="n"/>
-      <c r="R47" s="172" t="n"/>
-      <c r="S47" s="172" t="n"/>
-      <c r="T47" s="172" t="n"/>
-      <c r="U47" s="172" t="n"/>
-      <c r="V47" s="172" t="n"/>
-      <c r="W47" s="172" t="n"/>
-      <c r="X47" s="172" t="n"/>
-      <c r="Y47" s="172" t="n"/>
-      <c r="Z47" s="172" t="n"/>
-      <c r="AA47" s="172" t="n"/>
-      <c r="AB47" s="172" t="n"/>
-      <c r="AC47" s="172" t="n"/>
-      <c r="AD47" s="172" t="n"/>
-      <c r="AE47" s="172" t="n"/>
-      <c r="AF47" s="172" t="n"/>
-      <c r="AG47" s="172" t="n"/>
-      <c r="AH47" s="172" t="n"/>
-      <c r="AI47" s="172" t="n"/>
-      <c r="AJ47" s="172" t="n"/>
-      <c r="AK47" s="172" t="n"/>
-      <c r="AL47" s="172" t="n"/>
-      <c r="AM47" s="172" t="n"/>
-      <c r="AN47" s="172" t="n"/>
-      <c r="AO47" s="172" t="n"/>
-      <c r="AP47" s="172" t="n"/>
-      <c r="AQ47" s="172" t="n"/>
-      <c r="AR47" s="172" t="n"/>
-      <c r="AS47" s="172" t="n"/>
-      <c r="AT47" s="172" t="n"/>
-      <c r="AU47" s="172" t="n"/>
-      <c r="AV47" s="172" t="n"/>
-      <c r="AW47" s="172" t="n"/>
-      <c r="AX47" s="172" t="n"/>
-      <c r="AY47" s="172" t="n"/>
-      <c r="AZ47" s="172" t="n"/>
-      <c r="BA47" s="172" t="n"/>
-      <c r="BB47" s="172" t="n"/>
-      <c r="BC47" s="172" t="n"/>
-      <c r="BD47" s="172" t="n"/>
-      <c r="BE47" s="172" t="n"/>
-      <c r="BF47" s="172" t="n"/>
-      <c r="BG47" s="172" t="n"/>
-      <c r="BH47" s="172" t="n"/>
-      <c r="BI47" s="172" t="n"/>
-      <c r="BJ47" s="172" t="n"/>
-      <c r="BK47" s="172" t="n"/>
-      <c r="BL47" s="172" t="n"/>
-      <c r="BM47" s="172" t="n"/>
-      <c r="BN47" s="172" t="n"/>
-      <c r="BO47" s="172" t="n"/>
-      <c r="BP47" s="172" t="n"/>
-      <c r="BQ47" s="172" t="n"/>
-      <c r="BR47" s="172" t="n"/>
-      <c r="BS47" s="172" t="n"/>
-      <c r="BT47" s="172" t="n"/>
-      <c r="BU47" s="172" t="n"/>
-      <c r="BV47" s="172" t="n"/>
-      <c r="BW47" s="172" t="n"/>
-      <c r="BX47" s="172" t="n"/>
-      <c r="BY47" s="172" t="n"/>
-      <c r="BZ47" s="172" t="n"/>
-      <c r="CA47" s="172" t="n"/>
-      <c r="CB47" s="172" t="n"/>
-      <c r="CC47" s="172" t="n"/>
-      <c r="CD47" s="172" t="n"/>
-      <c r="CE47" s="172" t="n"/>
-      <c r="CF47" s="172" t="n"/>
-      <c r="CG47" s="172" t="n"/>
-      <c r="CH47" s="172" t="n"/>
-      <c r="CI47" s="172" t="n"/>
-      <c r="CJ47" s="172" t="n"/>
-      <c r="CK47" s="172" t="n"/>
-      <c r="CL47" s="172" t="n"/>
-      <c r="CM47" s="172" t="n"/>
-      <c r="CN47" s="172" t="n"/>
-      <c r="CO47" s="172" t="n"/>
-      <c r="CP47" s="172" t="n"/>
-      <c r="CQ47" s="172" t="n"/>
-      <c r="CR47" s="172" t="n"/>
-      <c r="CS47" s="172" t="n"/>
-      <c r="CT47" s="172" t="n"/>
-      <c r="CU47" s="172" t="n"/>
-      <c r="CV47" s="172" t="n"/>
-      <c r="CW47" s="172" t="n"/>
-      <c r="CX47" s="172" t="n"/>
-      <c r="CY47" s="172" t="n"/>
-      <c r="CZ47" s="172" t="n"/>
-      <c r="DA47" s="172" t="n"/>
-      <c r="DB47" s="172" t="n"/>
-      <c r="DC47" s="172" t="n"/>
-      <c r="DD47" s="172" t="n"/>
-      <c r="DE47" s="172" t="n"/>
-      <c r="DF47" s="172" t="n"/>
-      <c r="DG47" s="172" t="n"/>
-      <c r="DH47" s="172" t="n"/>
-      <c r="DI47" s="172" t="n"/>
-      <c r="DJ47" s="172" t="n"/>
-      <c r="DK47" s="172" t="n"/>
-      <c r="DL47" s="172" t="n"/>
-      <c r="DM47" s="172" t="n"/>
-      <c r="DN47" s="172" t="n"/>
-      <c r="DO47" s="172" t="n"/>
-      <c r="DP47" s="172" t="n"/>
-      <c r="DQ47" s="172" t="n"/>
-      <c r="DR47" s="172" t="n"/>
-      <c r="DS47" s="172" t="n"/>
-      <c r="DT47" s="172" t="n"/>
-      <c r="DU47" s="172" t="n"/>
-      <c r="DV47" s="172" t="n"/>
-      <c r="DW47" s="172" t="n"/>
-      <c r="DX47" s="172" t="n"/>
-      <c r="DY47" s="172" t="n"/>
-      <c r="DZ47" s="172" t="n"/>
-      <c r="EA47" s="172" t="n"/>
-      <c r="EB47" s="172" t="n"/>
-      <c r="EC47" s="172" t="n"/>
-      <c r="ED47" s="172" t="n"/>
-      <c r="EE47" s="172" t="n"/>
-      <c r="EF47" s="172" t="n"/>
-      <c r="EG47" s="172" t="n"/>
-      <c r="EH47" s="172" t="n"/>
-      <c r="EI47" s="172" t="n"/>
-      <c r="EJ47" s="172" t="n"/>
-      <c r="EK47" s="172" t="n"/>
-      <c r="EL47" s="172" t="n"/>
-      <c r="EM47" s="172" t="n"/>
-      <c r="EN47" s="172" t="n"/>
-      <c r="EO47" s="172" t="n"/>
-      <c r="EP47" s="172" t="n"/>
-      <c r="EQ47" s="172" t="n"/>
-      <c r="ER47" s="172" t="n"/>
-      <c r="ES47" s="172" t="n"/>
-      <c r="ET47" s="172" t="n"/>
-      <c r="EU47" s="172" t="n"/>
-      <c r="EV47" s="172" t="n"/>
-      <c r="EW47" s="172" t="n"/>
-      <c r="EX47" s="172" t="n"/>
-      <c r="EY47" s="172" t="n"/>
-      <c r="EZ47" s="172" t="n"/>
-      <c r="FA47" s="172" t="n"/>
-      <c r="FB47" s="172" t="n"/>
-      <c r="FC47" s="172" t="n"/>
-      <c r="FD47" s="172" t="n"/>
-      <c r="FE47" s="172" t="n"/>
-      <c r="FF47" s="172" t="n"/>
-      <c r="FG47" s="172" t="n"/>
-      <c r="FH47" s="172" t="n"/>
-      <c r="FI47" s="172" t="n"/>
-      <c r="FJ47" s="172" t="n"/>
-      <c r="FK47" s="172" t="n"/>
-      <c r="FL47" s="172" t="n"/>
-      <c r="FM47" s="172" t="n"/>
-      <c r="FN47" s="172" t="n"/>
-      <c r="FO47" s="172" t="n"/>
-      <c r="FP47" s="172" t="n"/>
-      <c r="FQ47" s="172" t="n"/>
-      <c r="FR47" s="172" t="n"/>
-      <c r="FS47" s="172" t="n"/>
-      <c r="FT47" s="172" t="n"/>
-      <c r="FU47" s="172" t="n"/>
-      <c r="FV47" s="172" t="n"/>
-      <c r="FW47" s="172" t="n"/>
-      <c r="FX47" s="172" t="n"/>
-      <c r="FY47" s="172" t="n"/>
-      <c r="FZ47" s="172" t="n"/>
-      <c r="GA47" s="172" t="n"/>
-      <c r="GB47" s="172" t="n"/>
-      <c r="GC47" s="172" t="n"/>
-      <c r="GD47" s="172" t="n"/>
-      <c r="GE47" s="172" t="n"/>
-      <c r="GF47" s="172" t="n"/>
+      <c r="D47" s="361" t="n"/>
+      <c r="E47" s="361" t="n"/>
+      <c r="F47" s="362" t="n"/>
+      <c r="G47" s="364" t="n"/>
+      <c r="H47" s="364" t="n"/>
+      <c r="I47" s="364" t="n"/>
+      <c r="J47" s="364" t="n"/>
+      <c r="K47" s="364" t="n"/>
+      <c r="L47" s="364" t="n"/>
+      <c r="M47" s="364" t="n"/>
+      <c r="N47" s="364" t="n"/>
+      <c r="O47" s="364" t="n"/>
+      <c r="P47" s="364" t="n"/>
+      <c r="Q47" s="364" t="n"/>
+      <c r="R47" s="364" t="n"/>
+      <c r="S47" s="364" t="n"/>
+      <c r="T47" s="364" t="n"/>
+      <c r="U47" s="364" t="n"/>
+      <c r="V47" s="364" t="n"/>
+      <c r="W47" s="364" t="n"/>
+      <c r="X47" s="364" t="n"/>
+      <c r="Y47" s="364" t="n"/>
+      <c r="Z47" s="364" t="n"/>
+      <c r="AA47" s="364" t="n"/>
+      <c r="AB47" s="364" t="n"/>
+      <c r="AC47" s="364" t="n"/>
+      <c r="AD47" s="364" t="n"/>
+      <c r="AE47" s="364" t="n"/>
+      <c r="AF47" s="364" t="n"/>
+      <c r="AG47" s="364" t="n"/>
+      <c r="AH47" s="364" t="n"/>
+      <c r="AI47" s="364" t="n"/>
+      <c r="AJ47" s="364" t="n"/>
+      <c r="AK47" s="364" t="n"/>
+      <c r="AL47" s="364" t="n"/>
+      <c r="AM47" s="364" t="n"/>
+      <c r="AN47" s="364" t="n"/>
+      <c r="AO47" s="364" t="n"/>
+      <c r="AP47" s="364" t="n"/>
+      <c r="AQ47" s="364" t="n"/>
+      <c r="AR47" s="364" t="n"/>
+      <c r="AS47" s="364" t="n"/>
+      <c r="AT47" s="364" t="n"/>
+      <c r="AU47" s="364" t="n"/>
+      <c r="AV47" s="364" t="n"/>
+      <c r="AW47" s="364" t="n"/>
+      <c r="AX47" s="364" t="n"/>
+      <c r="AY47" s="364" t="n"/>
+      <c r="AZ47" s="364" t="n"/>
+      <c r="BA47" s="364" t="n"/>
+      <c r="BB47" s="364" t="n"/>
+      <c r="BC47" s="364" t="n"/>
+      <c r="BD47" s="364" t="n"/>
+      <c r="BE47" s="364" t="n"/>
+      <c r="BF47" s="364" t="n"/>
+      <c r="BG47" s="364" t="n"/>
+      <c r="BH47" s="364" t="n"/>
+      <c r="BI47" s="364" t="n"/>
+      <c r="BJ47" s="364" t="n"/>
+      <c r="BK47" s="364" t="n"/>
+      <c r="BL47" s="364" t="n"/>
+      <c r="BM47" s="364" t="n"/>
+      <c r="BN47" s="364" t="n"/>
+      <c r="BO47" s="364" t="n"/>
+      <c r="BP47" s="364" t="n"/>
+      <c r="BQ47" s="364" t="n"/>
+      <c r="BR47" s="364" t="n"/>
+      <c r="BS47" s="364" t="n"/>
+      <c r="BT47" s="364" t="n"/>
+      <c r="BU47" s="364" t="n"/>
+      <c r="BV47" s="364" t="n"/>
+      <c r="BW47" s="364" t="n"/>
+      <c r="BX47" s="364" t="n"/>
+      <c r="BY47" s="364" t="n"/>
+      <c r="BZ47" s="364" t="n"/>
+      <c r="CA47" s="364" t="n"/>
+      <c r="CB47" s="364" t="n"/>
+      <c r="CC47" s="364" t="n"/>
+      <c r="CD47" s="364" t="n"/>
+      <c r="CE47" s="364" t="n"/>
+      <c r="CF47" s="364" t="n"/>
+      <c r="CG47" s="364" t="n"/>
+      <c r="CH47" s="364" t="n"/>
+      <c r="CI47" s="364" t="n"/>
+      <c r="CJ47" s="364" t="n"/>
+      <c r="CK47" s="364" t="n"/>
+      <c r="CL47" s="364" t="n"/>
+      <c r="CM47" s="364" t="n"/>
+      <c r="CN47" s="364" t="n"/>
+      <c r="CO47" s="364" t="n"/>
+      <c r="CP47" s="364" t="n"/>
+      <c r="CQ47" s="364" t="n"/>
+      <c r="CR47" s="364" t="n"/>
+      <c r="CS47" s="364" t="n"/>
+      <c r="CT47" s="364" t="n"/>
+      <c r="CU47" s="364" t="n"/>
+      <c r="CV47" s="364" t="n"/>
+      <c r="CW47" s="364" t="n"/>
+      <c r="CX47" s="364" t="n"/>
+      <c r="CY47" s="364" t="n"/>
+      <c r="CZ47" s="364" t="n"/>
+      <c r="DA47" s="364" t="n"/>
+      <c r="DB47" s="364" t="n"/>
+      <c r="DC47" s="364" t="n"/>
+      <c r="DD47" s="364" t="n"/>
+      <c r="DE47" s="364" t="n"/>
+      <c r="DF47" s="364" t="n"/>
+      <c r="DG47" s="364" t="n"/>
+      <c r="DH47" s="364" t="n"/>
+      <c r="DI47" s="364" t="n"/>
+      <c r="DJ47" s="364" t="n"/>
+      <c r="DK47" s="364" t="n"/>
+      <c r="DL47" s="364" t="n"/>
+      <c r="DM47" s="364" t="n"/>
+      <c r="DN47" s="364" t="n"/>
+      <c r="DO47" s="364" t="n"/>
+      <c r="DP47" s="364" t="n"/>
+      <c r="DQ47" s="364" t="n"/>
+      <c r="DR47" s="364" t="n"/>
+      <c r="DS47" s="364" t="n"/>
+      <c r="DT47" s="364" t="n"/>
+      <c r="DU47" s="364" t="n"/>
+      <c r="DV47" s="364" t="n"/>
+      <c r="DW47" s="364" t="n"/>
+      <c r="DX47" s="364" t="n"/>
+      <c r="DY47" s="364" t="n"/>
+      <c r="DZ47" s="364" t="n"/>
+      <c r="EA47" s="364" t="n"/>
+      <c r="EB47" s="364" t="n"/>
+      <c r="EC47" s="364" t="n"/>
+      <c r="ED47" s="364" t="n"/>
+      <c r="EE47" s="364" t="n"/>
+      <c r="EF47" s="364" t="n"/>
+      <c r="EG47" s="364" t="n"/>
+      <c r="EH47" s="364" t="n"/>
+      <c r="EI47" s="364" t="n"/>
+      <c r="EJ47" s="364" t="n"/>
+      <c r="EK47" s="364" t="n"/>
+      <c r="EL47" s="364" t="n"/>
+      <c r="EM47" s="364" t="n"/>
+      <c r="EN47" s="364" t="n"/>
+      <c r="EO47" s="364" t="n"/>
+      <c r="EP47" s="364" t="n"/>
+      <c r="EQ47" s="364" t="n"/>
+      <c r="ER47" s="364" t="n"/>
+      <c r="ES47" s="364" t="n"/>
+      <c r="ET47" s="364" t="n"/>
+      <c r="EU47" s="364" t="n"/>
+      <c r="EV47" s="364" t="n"/>
+      <c r="EW47" s="364" t="n"/>
+      <c r="EX47" s="364" t="n"/>
+      <c r="EY47" s="364" t="n"/>
+      <c r="EZ47" s="364" t="n"/>
+      <c r="FA47" s="364" t="n"/>
+      <c r="FB47" s="364" t="n"/>
+      <c r="FC47" s="364" t="n"/>
+      <c r="FD47" s="431" t="n"/>
+      <c r="FE47" s="431" t="n"/>
+      <c r="FF47" s="431" t="n"/>
+      <c r="FG47" s="431" t="n"/>
+      <c r="FH47" s="431" t="n"/>
+      <c r="FI47" s="364" t="n"/>
+      <c r="FJ47" s="364" t="n"/>
+      <c r="FK47" s="364" t="n"/>
+      <c r="FL47" s="364" t="n"/>
+      <c r="FM47" s="364" t="n"/>
+      <c r="FN47" s="364" t="n"/>
+      <c r="FO47" s="364" t="n"/>
+      <c r="FP47" s="364" t="n"/>
+      <c r="FQ47" s="364" t="n"/>
+      <c r="FR47" s="364" t="n"/>
+      <c r="FS47" s="364" t="n"/>
+      <c r="FT47" s="364" t="n"/>
+      <c r="FU47" s="364" t="n"/>
+      <c r="FV47" s="364" t="n"/>
+      <c r="FW47" s="364" t="n"/>
+      <c r="FX47" s="364" t="n"/>
+      <c r="FY47" s="364" t="n"/>
+      <c r="FZ47" s="364" t="n"/>
+      <c r="GA47" s="364" t="n"/>
+      <c r="GB47" s="364" t="n"/>
+      <c r="GC47" s="364" t="n"/>
+      <c r="GD47" s="364" t="n"/>
+      <c r="GE47" s="364" t="n"/>
+      <c r="GF47" s="364" t="n"/>
       <c r="GG47" s="364" t="n"/>
       <c r="GH47" s="364" t="n"/>
       <c r="GI47" s="364" t="n"/>
@@ -15165,199 +15183,199 @@
       <c r="HN47" s="364" t="n"/>
       <c r="HO47" s="364" t="n"/>
     </row>
-    <row r="48" ht="15.75" customHeight="1" s="173">
-      <c r="A48" s="156" t="n"/>
-      <c r="B48" s="405" t="n"/>
-      <c r="C48" s="404" t="inlineStr">
+    <row r="48" ht="32" customHeight="1" s="173">
+      <c r="A48" s="364" t="n"/>
+      <c r="B48" s="425" t="inlineStr"/>
+      <c r="C48" s="424" t="inlineStr">
         <is>
-          <t>마일스톤 / 기준선</t>
+          <t>종료 감리</t>
         </is>
       </c>
-      <c r="D48" s="364" t="n"/>
-      <c r="E48" s="364" t="n"/>
-      <c r="F48" s="364" t="n"/>
-      <c r="G48" s="172" t="n"/>
-      <c r="H48" s="172" t="n"/>
-      <c r="I48" s="172" t="n"/>
-      <c r="J48" s="172" t="n"/>
-      <c r="K48" s="172" t="n"/>
-      <c r="L48" s="172" t="n"/>
-      <c r="M48" s="172" t="n"/>
-      <c r="N48" s="172" t="n"/>
-      <c r="O48" s="172" t="n"/>
-      <c r="P48" s="172" t="n"/>
-      <c r="Q48" s="172" t="n"/>
-      <c r="R48" s="172" t="n"/>
-      <c r="S48" s="172" t="n"/>
-      <c r="T48" s="172" t="n"/>
-      <c r="U48" s="172" t="n"/>
-      <c r="V48" s="172" t="n"/>
-      <c r="W48" s="172" t="n"/>
-      <c r="X48" s="172" t="n"/>
-      <c r="Y48" s="172" t="n"/>
-      <c r="Z48" s="172" t="n"/>
-      <c r="AA48" s="172" t="n"/>
-      <c r="AB48" s="172" t="n"/>
-      <c r="AC48" s="172" t="n"/>
-      <c r="AD48" s="172" t="n"/>
-      <c r="AE48" s="172" t="n"/>
-      <c r="AF48" s="172" t="n"/>
-      <c r="AG48" s="172" t="n"/>
-      <c r="AH48" s="172" t="n"/>
-      <c r="AI48" s="172" t="n"/>
-      <c r="AJ48" s="172" t="n"/>
-      <c r="AK48" s="172" t="n"/>
-      <c r="AL48" s="172" t="n"/>
-      <c r="AM48" s="172" t="n"/>
-      <c r="AN48" s="172" t="n"/>
-      <c r="AO48" s="172" t="n"/>
-      <c r="AP48" s="172" t="n"/>
-      <c r="AQ48" s="172" t="n"/>
-      <c r="AR48" s="172" t="n"/>
-      <c r="AS48" s="172" t="n"/>
-      <c r="AT48" s="172" t="n"/>
-      <c r="AU48" s="172" t="n"/>
-      <c r="AV48" s="172" t="n"/>
-      <c r="AW48" s="172" t="n"/>
-      <c r="AX48" s="172" t="n"/>
-      <c r="AY48" s="172" t="n"/>
-      <c r="AZ48" s="172" t="n"/>
-      <c r="BA48" s="172" t="n"/>
-      <c r="BB48" s="172" t="n"/>
-      <c r="BC48" s="172" t="n"/>
-      <c r="BD48" s="172" t="n"/>
-      <c r="BE48" s="172" t="n"/>
-      <c r="BF48" s="172" t="n"/>
-      <c r="BG48" s="172" t="n"/>
-      <c r="BH48" s="172" t="n"/>
-      <c r="BI48" s="172" t="n"/>
-      <c r="BJ48" s="172" t="n"/>
-      <c r="BK48" s="172" t="n"/>
-      <c r="BL48" s="172" t="n"/>
-      <c r="BM48" s="172" t="n"/>
-      <c r="BN48" s="172" t="n"/>
-      <c r="BO48" s="172" t="n"/>
-      <c r="BP48" s="172" t="n"/>
-      <c r="BQ48" s="172" t="n"/>
-      <c r="BR48" s="172" t="n"/>
-      <c r="BS48" s="172" t="n"/>
-      <c r="BT48" s="172" t="n"/>
-      <c r="BU48" s="172" t="n"/>
-      <c r="BV48" s="172" t="n"/>
-      <c r="BW48" s="172" t="n"/>
-      <c r="BX48" s="172" t="n"/>
-      <c r="BY48" s="172" t="n"/>
-      <c r="BZ48" s="172" t="n"/>
-      <c r="CA48" s="172" t="n"/>
-      <c r="CB48" s="172" t="n"/>
-      <c r="CC48" s="172" t="n"/>
-      <c r="CD48" s="172" t="n"/>
-      <c r="CE48" s="172" t="n"/>
-      <c r="CF48" s="172" t="n"/>
-      <c r="CG48" s="172" t="n"/>
-      <c r="CH48" s="172" t="n"/>
-      <c r="CI48" s="172" t="n"/>
-      <c r="CJ48" s="172" t="n"/>
-      <c r="CK48" s="172" t="n"/>
-      <c r="CL48" s="172" t="n"/>
-      <c r="CM48" s="172" t="n"/>
-      <c r="CN48" s="172" t="n"/>
-      <c r="CO48" s="172" t="n"/>
-      <c r="CP48" s="172" t="n"/>
-      <c r="CQ48" s="172" t="n"/>
-      <c r="CR48" s="172" t="n"/>
-      <c r="CS48" s="172" t="n"/>
-      <c r="CT48" s="172" t="n"/>
-      <c r="CU48" s="172" t="n"/>
-      <c r="CV48" s="172" t="n"/>
-      <c r="CW48" s="172" t="n"/>
-      <c r="CX48" s="172" t="n"/>
-      <c r="CY48" s="172" t="n"/>
-      <c r="CZ48" s="172" t="n"/>
-      <c r="DA48" s="172" t="n"/>
-      <c r="DB48" s="172" t="n"/>
-      <c r="DC48" s="172" t="n"/>
-      <c r="DD48" s="172" t="n"/>
-      <c r="DE48" s="172" t="n"/>
-      <c r="DF48" s="172" t="n"/>
-      <c r="DG48" s="172" t="n"/>
-      <c r="DH48" s="172" t="n"/>
-      <c r="DI48" s="172" t="n"/>
-      <c r="DJ48" s="172" t="n"/>
-      <c r="DK48" s="172" t="n"/>
-      <c r="DL48" s="172" t="n"/>
-      <c r="DM48" s="172" t="n"/>
-      <c r="DN48" s="172" t="n"/>
-      <c r="DO48" s="172" t="n"/>
-      <c r="DP48" s="172" t="n"/>
-      <c r="DQ48" s="172" t="n"/>
-      <c r="DR48" s="172" t="n"/>
-      <c r="DS48" s="172" t="n"/>
-      <c r="DT48" s="172" t="n"/>
-      <c r="DU48" s="172" t="n"/>
-      <c r="DV48" s="172" t="n"/>
-      <c r="DW48" s="172" t="n"/>
-      <c r="DX48" s="172" t="n"/>
-      <c r="DY48" s="172" t="n"/>
-      <c r="DZ48" s="172" t="n"/>
-      <c r="EA48" s="172" t="n"/>
-      <c r="EB48" s="172" t="n"/>
-      <c r="EC48" s="172" t="n"/>
-      <c r="ED48" s="172" t="n"/>
-      <c r="EE48" s="172" t="n"/>
-      <c r="EF48" s="172" t="n"/>
-      <c r="EG48" s="172" t="n"/>
-      <c r="EH48" s="172" t="n"/>
-      <c r="EI48" s="172" t="n"/>
-      <c r="EJ48" s="172" t="n"/>
-      <c r="EK48" s="172" t="n"/>
-      <c r="EL48" s="172" t="n"/>
-      <c r="EM48" s="172" t="n"/>
-      <c r="EN48" s="172" t="n"/>
-      <c r="EO48" s="172" t="n"/>
-      <c r="EP48" s="172" t="n"/>
-      <c r="EQ48" s="172" t="n"/>
-      <c r="ER48" s="172" t="n"/>
-      <c r="ES48" s="172" t="n"/>
-      <c r="ET48" s="172" t="n"/>
-      <c r="EU48" s="172" t="n"/>
-      <c r="EV48" s="172" t="n"/>
-      <c r="EW48" s="172" t="n"/>
-      <c r="EX48" s="172" t="n"/>
-      <c r="EY48" s="172" t="n"/>
-      <c r="EZ48" s="172" t="n"/>
-      <c r="FA48" s="172" t="n"/>
-      <c r="FB48" s="172" t="n"/>
-      <c r="FC48" s="172" t="n"/>
-      <c r="FD48" s="172" t="n"/>
-      <c r="FE48" s="172" t="n"/>
-      <c r="FF48" s="172" t="n"/>
-      <c r="FG48" s="172" t="n"/>
-      <c r="FH48" s="172" t="n"/>
-      <c r="FI48" s="172" t="n"/>
-      <c r="FJ48" s="172" t="n"/>
-      <c r="FK48" s="172" t="n"/>
-      <c r="FL48" s="172" t="n"/>
-      <c r="FM48" s="172" t="n"/>
-      <c r="FN48" s="172" t="n"/>
-      <c r="FO48" s="172" t="n"/>
-      <c r="FP48" s="172" t="n"/>
-      <c r="FQ48" s="172" t="n"/>
-      <c r="FR48" s="172" t="n"/>
-      <c r="FS48" s="172" t="n"/>
-      <c r="FT48" s="172" t="n"/>
-      <c r="FU48" s="172" t="n"/>
-      <c r="FV48" s="172" t="n"/>
-      <c r="FW48" s="172" t="n"/>
-      <c r="FX48" s="172" t="n"/>
-      <c r="FY48" s="172" t="n"/>
-      <c r="FZ48" s="172" t="n"/>
-      <c r="GA48" s="172" t="n"/>
-      <c r="GB48" s="172" t="n"/>
-      <c r="GC48" s="172" t="n"/>
-      <c r="GD48" s="172" t="n"/>
-      <c r="GE48" s="172" t="n"/>
-      <c r="GF48" s="172" t="n"/>
+      <c r="D48" s="361" t="n"/>
+      <c r="E48" s="361" t="n"/>
+      <c r="F48" s="362" t="n"/>
+      <c r="G48" s="364" t="n"/>
+      <c r="H48" s="364" t="n"/>
+      <c r="I48" s="364" t="n"/>
+      <c r="J48" s="364" t="n"/>
+      <c r="K48" s="364" t="n"/>
+      <c r="L48" s="364" t="n"/>
+      <c r="M48" s="364" t="n"/>
+      <c r="N48" s="364" t="n"/>
+      <c r="O48" s="364" t="n"/>
+      <c r="P48" s="364" t="n"/>
+      <c r="Q48" s="364" t="n"/>
+      <c r="R48" s="364" t="n"/>
+      <c r="S48" s="364" t="n"/>
+      <c r="T48" s="364" t="n"/>
+      <c r="U48" s="364" t="n"/>
+      <c r="V48" s="364" t="n"/>
+      <c r="W48" s="364" t="n"/>
+      <c r="X48" s="364" t="n"/>
+      <c r="Y48" s="364" t="n"/>
+      <c r="Z48" s="364" t="n"/>
+      <c r="AA48" s="364" t="n"/>
+      <c r="AB48" s="364" t="n"/>
+      <c r="AC48" s="364" t="n"/>
+      <c r="AD48" s="364" t="n"/>
+      <c r="AE48" s="364" t="n"/>
+      <c r="AF48" s="364" t="n"/>
+      <c r="AG48" s="364" t="n"/>
+      <c r="AH48" s="364" t="n"/>
+      <c r="AI48" s="364" t="n"/>
+      <c r="AJ48" s="364" t="n"/>
+      <c r="AK48" s="364" t="n"/>
+      <c r="AL48" s="364" t="n"/>
+      <c r="AM48" s="364" t="n"/>
+      <c r="AN48" s="364" t="n"/>
+      <c r="AO48" s="364" t="n"/>
+      <c r="AP48" s="364" t="n"/>
+      <c r="AQ48" s="364" t="n"/>
+      <c r="AR48" s="364" t="n"/>
+      <c r="AS48" s="364" t="n"/>
+      <c r="AT48" s="364" t="n"/>
+      <c r="AU48" s="364" t="n"/>
+      <c r="AV48" s="364" t="n"/>
+      <c r="AW48" s="364" t="n"/>
+      <c r="AX48" s="364" t="n"/>
+      <c r="AY48" s="364" t="n"/>
+      <c r="AZ48" s="364" t="n"/>
+      <c r="BA48" s="364" t="n"/>
+      <c r="BB48" s="364" t="n"/>
+      <c r="BC48" s="364" t="n"/>
+      <c r="BD48" s="364" t="n"/>
+      <c r="BE48" s="364" t="n"/>
+      <c r="BF48" s="364" t="n"/>
+      <c r="BG48" s="364" t="n"/>
+      <c r="BH48" s="364" t="n"/>
+      <c r="BI48" s="364" t="n"/>
+      <c r="BJ48" s="364" t="n"/>
+      <c r="BK48" s="364" t="n"/>
+      <c r="BL48" s="364" t="n"/>
+      <c r="BM48" s="364" t="n"/>
+      <c r="BN48" s="364" t="n"/>
+      <c r="BO48" s="364" t="n"/>
+      <c r="BP48" s="364" t="n"/>
+      <c r="BQ48" s="364" t="n"/>
+      <c r="BR48" s="364" t="n"/>
+      <c r="BS48" s="364" t="n"/>
+      <c r="BT48" s="364" t="n"/>
+      <c r="BU48" s="364" t="n"/>
+      <c r="BV48" s="364" t="n"/>
+      <c r="BW48" s="364" t="n"/>
+      <c r="BX48" s="364" t="n"/>
+      <c r="BY48" s="364" t="n"/>
+      <c r="BZ48" s="364" t="n"/>
+      <c r="CA48" s="364" t="n"/>
+      <c r="CB48" s="364" t="n"/>
+      <c r="CC48" s="364" t="n"/>
+      <c r="CD48" s="364" t="n"/>
+      <c r="CE48" s="364" t="n"/>
+      <c r="CF48" s="364" t="n"/>
+      <c r="CG48" s="364" t="n"/>
+      <c r="CH48" s="364" t="n"/>
+      <c r="CI48" s="364" t="n"/>
+      <c r="CJ48" s="364" t="n"/>
+      <c r="CK48" s="364" t="n"/>
+      <c r="CL48" s="364" t="n"/>
+      <c r="CM48" s="364" t="n"/>
+      <c r="CN48" s="364" t="n"/>
+      <c r="CO48" s="364" t="n"/>
+      <c r="CP48" s="364" t="n"/>
+      <c r="CQ48" s="364" t="n"/>
+      <c r="CR48" s="364" t="n"/>
+      <c r="CS48" s="364" t="n"/>
+      <c r="CT48" s="364" t="n"/>
+      <c r="CU48" s="364" t="n"/>
+      <c r="CV48" s="364" t="n"/>
+      <c r="CW48" s="364" t="n"/>
+      <c r="CX48" s="364" t="n"/>
+      <c r="CY48" s="364" t="n"/>
+      <c r="CZ48" s="364" t="n"/>
+      <c r="DA48" s="364" t="n"/>
+      <c r="DB48" s="364" t="n"/>
+      <c r="DC48" s="364" t="n"/>
+      <c r="DD48" s="364" t="n"/>
+      <c r="DE48" s="364" t="n"/>
+      <c r="DF48" s="364" t="n"/>
+      <c r="DG48" s="364" t="n"/>
+      <c r="DH48" s="364" t="n"/>
+      <c r="DI48" s="364" t="n"/>
+      <c r="DJ48" s="364" t="n"/>
+      <c r="DK48" s="364" t="n"/>
+      <c r="DL48" s="364" t="n"/>
+      <c r="DM48" s="364" t="n"/>
+      <c r="DN48" s="364" t="n"/>
+      <c r="DO48" s="364" t="n"/>
+      <c r="DP48" s="364" t="n"/>
+      <c r="DQ48" s="364" t="n"/>
+      <c r="DR48" s="364" t="n"/>
+      <c r="DS48" s="364" t="n"/>
+      <c r="DT48" s="364" t="n"/>
+      <c r="DU48" s="364" t="n"/>
+      <c r="DV48" s="364" t="n"/>
+      <c r="DW48" s="364" t="n"/>
+      <c r="DX48" s="364" t="n"/>
+      <c r="DY48" s="364" t="n"/>
+      <c r="DZ48" s="364" t="n"/>
+      <c r="EA48" s="364" t="n"/>
+      <c r="EB48" s="364" t="n"/>
+      <c r="EC48" s="364" t="n"/>
+      <c r="ED48" s="364" t="n"/>
+      <c r="EE48" s="364" t="n"/>
+      <c r="EF48" s="364" t="n"/>
+      <c r="EG48" s="364" t="n"/>
+      <c r="EH48" s="364" t="n"/>
+      <c r="EI48" s="364" t="n"/>
+      <c r="EJ48" s="364" t="n"/>
+      <c r="EK48" s="364" t="n"/>
+      <c r="EL48" s="364" t="n"/>
+      <c r="EM48" s="364" t="n"/>
+      <c r="EN48" s="364" t="n"/>
+      <c r="EO48" s="364" t="n"/>
+      <c r="EP48" s="364" t="n"/>
+      <c r="EQ48" s="364" t="n"/>
+      <c r="ER48" s="364" t="n"/>
+      <c r="ES48" s="364" t="n"/>
+      <c r="ET48" s="364" t="n"/>
+      <c r="EU48" s="364" t="n"/>
+      <c r="EV48" s="364" t="n"/>
+      <c r="EW48" s="364" t="n"/>
+      <c r="EX48" s="364" t="n"/>
+      <c r="EY48" s="364" t="n"/>
+      <c r="EZ48" s="364" t="n"/>
+      <c r="FA48" s="364" t="n"/>
+      <c r="FB48" s="364" t="n"/>
+      <c r="FC48" s="364" t="n"/>
+      <c r="FD48" s="364" t="n"/>
+      <c r="FE48" s="364" t="n"/>
+      <c r="FF48" s="364" t="n"/>
+      <c r="FG48" s="364" t="n"/>
+      <c r="FH48" s="364" t="n"/>
+      <c r="FI48" s="364" t="n"/>
+      <c r="FJ48" s="364" t="n"/>
+      <c r="FK48" s="364" t="n"/>
+      <c r="FL48" s="364" t="n"/>
+      <c r="FM48" s="364" t="n"/>
+      <c r="FN48" s="364" t="n"/>
+      <c r="FO48" s="364" t="n"/>
+      <c r="FP48" s="364" t="n"/>
+      <c r="FQ48" s="364" t="n"/>
+      <c r="FR48" s="364" t="n"/>
+      <c r="FS48" s="364" t="n"/>
+      <c r="FT48" s="364" t="n"/>
+      <c r="FU48" s="364" t="n"/>
+      <c r="FV48" s="364" t="n"/>
+      <c r="FW48" s="364" t="n"/>
+      <c r="FX48" s="364" t="n"/>
+      <c r="FY48" s="431" t="n"/>
+      <c r="FZ48" s="431" t="n"/>
+      <c r="GA48" s="431" t="n"/>
+      <c r="GB48" s="431" t="n"/>
+      <c r="GC48" s="431" t="n"/>
+      <c r="GD48" s="364" t="n"/>
+      <c r="GE48" s="364" t="n"/>
+      <c r="GF48" s="364" t="n"/>
       <c r="GG48" s="364" t="n"/>
       <c r="GH48" s="364" t="n"/>
       <c r="GI48" s="364" t="n"/>
@@ -15396,12 +15414,8 @@
     </row>
     <row r="49" ht="15.75" customHeight="1" s="173">
       <c r="A49" s="156" t="n"/>
-      <c r="B49" s="406" t="n"/>
-      <c r="C49" s="404" t="inlineStr">
-        <is>
-          <t>예정 — 데이터 검수 · 최종 검증 · 완료 보고</t>
-        </is>
-      </c>
+      <c r="B49" s="156" t="n"/>
+      <c r="C49" s="156" t="n"/>
       <c r="D49" s="364" t="n"/>
       <c r="E49" s="364" t="n"/>
       <c r="F49" s="364" t="n"/>
@@ -15625,12 +15639,12 @@
     </row>
     <row r="50" ht="15.75" customHeight="1" s="173">
       <c r="A50" s="156" t="n"/>
-      <c r="B50" s="412" t="n"/>
-      <c r="C50" s="404" t="inlineStr">
+      <c r="B50" s="402" t="inlineStr">
         <is>
-          <t>예정 — 배포 준비 · 시스템 연계</t>
+          <t>■ 범례</t>
         </is>
       </c>
+      <c r="C50" s="364" t="n"/>
       <c r="D50" s="364" t="n"/>
       <c r="E50" s="364" t="n"/>
       <c r="F50" s="364" t="n"/>
@@ -15854,10 +15868,10 @@
     </row>
     <row r="51" ht="15.75" customHeight="1" s="173">
       <c r="A51" s="156" t="n"/>
-      <c r="B51" s="413" t="n"/>
+      <c r="B51" s="403" t="n"/>
       <c r="C51" s="404" t="inlineStr">
         <is>
-          <t>예정 — KL API 협의 · 베타 · 감리</t>
+          <t>완료 (작업 완료 · 1차 완료)</t>
         </is>
       </c>
       <c r="D51" s="364" t="n"/>
@@ -16083,8 +16097,15 @@
     </row>
     <row r="52" ht="15.75" customHeight="1" s="173">
       <c r="A52" s="156" t="n"/>
-      <c r="B52" s="156" t="n"/>
-      <c r="C52" s="404" t="n"/>
+      <c r="B52" s="405" t="n"/>
+      <c r="C52" s="404" t="inlineStr">
+        <is>
+          <t>마일스톤 / 기준선</t>
+        </is>
+      </c>
+      <c r="D52" s="364" t="n"/>
+      <c r="E52" s="364" t="n"/>
+      <c r="F52" s="364" t="n"/>
       <c r="G52" s="172" t="n"/>
       <c r="H52" s="172" t="n"/>
       <c r="I52" s="172" t="n"/>
@@ -16267,11 +16288,50 @@
       <c r="GD52" s="172" t="n"/>
       <c r="GE52" s="172" t="n"/>
       <c r="GF52" s="172" t="n"/>
+      <c r="GG52" s="364" t="n"/>
+      <c r="GH52" s="364" t="n"/>
+      <c r="GI52" s="364" t="n"/>
+      <c r="GJ52" s="364" t="n"/>
+      <c r="GK52" s="364" t="n"/>
+      <c r="GL52" s="364" t="n"/>
+      <c r="GM52" s="364" t="n"/>
+      <c r="GN52" s="364" t="n"/>
+      <c r="GO52" s="364" t="n"/>
+      <c r="GP52" s="364" t="n"/>
+      <c r="GQ52" s="364" t="n"/>
+      <c r="GR52" s="364" t="n"/>
+      <c r="GS52" s="364" t="n"/>
+      <c r="GT52" s="364" t="n"/>
+      <c r="GU52" s="364" t="n"/>
+      <c r="GV52" s="364" t="n"/>
+      <c r="GW52" s="364" t="n"/>
+      <c r="GX52" s="364" t="n"/>
+      <c r="GY52" s="364" t="n"/>
+      <c r="GZ52" s="364" t="n"/>
+      <c r="HA52" s="364" t="n"/>
+      <c r="HB52" s="364" t="n"/>
+      <c r="HC52" s="364" t="n"/>
+      <c r="HD52" s="364" t="n"/>
+      <c r="HE52" s="364" t="n"/>
+      <c r="HF52" s="364" t="n"/>
+      <c r="HG52" s="364" t="n"/>
+      <c r="HH52" s="364" t="n"/>
+      <c r="HI52" s="364" t="n"/>
+      <c r="HJ52" s="364" t="n"/>
+      <c r="HK52" s="364" t="n"/>
+      <c r="HL52" s="364" t="n"/>
+      <c r="HM52" s="364" t="n"/>
+      <c r="HN52" s="364" t="n"/>
+      <c r="HO52" s="364" t="n"/>
     </row>
     <row r="53" ht="15.75" customHeight="1" s="173">
       <c r="A53" s="156" t="n"/>
-      <c r="B53" s="156" t="n"/>
-      <c r="C53" s="404" t="n"/>
+      <c r="B53" s="406" t="n"/>
+      <c r="C53" s="404" t="inlineStr">
+        <is>
+          <t>예정 — 데이터 검수 · 최종 검증 · 완료 보고</t>
+        </is>
+      </c>
       <c r="G53" s="172" t="n"/>
       <c r="H53" s="172" t="n"/>
       <c r="I53" s="172" t="n"/>
@@ -16454,14 +16514,50 @@
       <c r="GD53" s="172" t="n"/>
       <c r="GE53" s="172" t="n"/>
       <c r="GF53" s="172" t="n"/>
+      <c r="GG53" s="364" t="n"/>
+      <c r="GH53" s="364" t="n"/>
+      <c r="GI53" s="364" t="n"/>
+      <c r="GJ53" s="364" t="n"/>
+      <c r="GK53" s="364" t="n"/>
+      <c r="GL53" s="364" t="n"/>
+      <c r="GM53" s="364" t="n"/>
+      <c r="GN53" s="364" t="n"/>
+      <c r="GO53" s="364" t="n"/>
+      <c r="GP53" s="364" t="n"/>
+      <c r="GQ53" s="364" t="n"/>
+      <c r="GR53" s="364" t="n"/>
+      <c r="GS53" s="364" t="n"/>
+      <c r="GT53" s="364" t="n"/>
+      <c r="GU53" s="364" t="n"/>
+      <c r="GV53" s="364" t="n"/>
+      <c r="GW53" s="364" t="n"/>
+      <c r="GX53" s="364" t="n"/>
+      <c r="GY53" s="364" t="n"/>
+      <c r="GZ53" s="364" t="n"/>
+      <c r="HA53" s="364" t="n"/>
+      <c r="HB53" s="364" t="n"/>
+      <c r="HC53" s="364" t="n"/>
+      <c r="HD53" s="364" t="n"/>
+      <c r="HE53" s="364" t="n"/>
+      <c r="HF53" s="364" t="n"/>
+      <c r="HG53" s="364" t="n"/>
+      <c r="HH53" s="364" t="n"/>
+      <c r="HI53" s="364" t="n"/>
+      <c r="HJ53" s="364" t="n"/>
+      <c r="HK53" s="364" t="n"/>
+      <c r="HL53" s="364" t="n"/>
+      <c r="HM53" s="364" t="n"/>
+      <c r="HN53" s="364" t="n"/>
+      <c r="HO53" s="364" t="n"/>
     </row>
     <row r="54" ht="15.75" customHeight="1" s="173">
       <c r="A54" s="156" t="n"/>
-      <c r="B54" s="156" t="n"/>
-      <c r="C54" s="156" t="n"/>
-      <c r="D54" s="171" t="n"/>
-      <c r="E54" s="171" t="n"/>
-      <c r="F54" s="156" t="n"/>
+      <c r="B54" s="412" t="n"/>
+      <c r="C54" s="404" t="inlineStr">
+        <is>
+          <t>예정 — 배포 준비 · 시스템 연계</t>
+        </is>
+      </c>
       <c r="G54" s="172" t="n"/>
       <c r="H54" s="172" t="n"/>
       <c r="I54" s="172" t="n"/>
@@ -16644,14 +16740,50 @@
       <c r="GD54" s="172" t="n"/>
       <c r="GE54" s="172" t="n"/>
       <c r="GF54" s="172" t="n"/>
+      <c r="GG54" s="364" t="n"/>
+      <c r="GH54" s="364" t="n"/>
+      <c r="GI54" s="364" t="n"/>
+      <c r="GJ54" s="364" t="n"/>
+      <c r="GK54" s="364" t="n"/>
+      <c r="GL54" s="364" t="n"/>
+      <c r="GM54" s="364" t="n"/>
+      <c r="GN54" s="364" t="n"/>
+      <c r="GO54" s="364" t="n"/>
+      <c r="GP54" s="364" t="n"/>
+      <c r="GQ54" s="364" t="n"/>
+      <c r="GR54" s="364" t="n"/>
+      <c r="GS54" s="364" t="n"/>
+      <c r="GT54" s="364" t="n"/>
+      <c r="GU54" s="364" t="n"/>
+      <c r="GV54" s="364" t="n"/>
+      <c r="GW54" s="364" t="n"/>
+      <c r="GX54" s="364" t="n"/>
+      <c r="GY54" s="364" t="n"/>
+      <c r="GZ54" s="364" t="n"/>
+      <c r="HA54" s="364" t="n"/>
+      <c r="HB54" s="364" t="n"/>
+      <c r="HC54" s="364" t="n"/>
+      <c r="HD54" s="364" t="n"/>
+      <c r="HE54" s="364" t="n"/>
+      <c r="HF54" s="364" t="n"/>
+      <c r="HG54" s="364" t="n"/>
+      <c r="HH54" s="364" t="n"/>
+      <c r="HI54" s="364" t="n"/>
+      <c r="HJ54" s="364" t="n"/>
+      <c r="HK54" s="364" t="n"/>
+      <c r="HL54" s="364" t="n"/>
+      <c r="HM54" s="364" t="n"/>
+      <c r="HN54" s="364" t="n"/>
+      <c r="HO54" s="364" t="n"/>
     </row>
     <row r="55" ht="15.75" customHeight="1" s="173">
       <c r="A55" s="156" t="n"/>
-      <c r="B55" s="156" t="n"/>
-      <c r="C55" s="156" t="n"/>
-      <c r="D55" s="171" t="n"/>
-      <c r="E55" s="171" t="n"/>
-      <c r="F55" s="156" t="n"/>
+      <c r="B55" s="413" t="n"/>
+      <c r="C55" s="404" t="inlineStr">
+        <is>
+          <t>예정 — KL API 협의 · 베타 · 감리</t>
+        </is>
+      </c>
       <c r="G55" s="172" t="n"/>
       <c r="H55" s="172" t="n"/>
       <c r="I55" s="172" t="n"/>
@@ -16834,14 +16966,46 @@
       <c r="GD55" s="172" t="n"/>
       <c r="GE55" s="172" t="n"/>
       <c r="GF55" s="172" t="n"/>
+      <c r="GG55" s="364" t="n"/>
+      <c r="GH55" s="364" t="n"/>
+      <c r="GI55" s="364" t="n"/>
+      <c r="GJ55" s="364" t="n"/>
+      <c r="GK55" s="364" t="n"/>
+      <c r="GL55" s="364" t="n"/>
+      <c r="GM55" s="364" t="n"/>
+      <c r="GN55" s="364" t="n"/>
+      <c r="GO55" s="364" t="n"/>
+      <c r="GP55" s="364" t="n"/>
+      <c r="GQ55" s="364" t="n"/>
+      <c r="GR55" s="364" t="n"/>
+      <c r="GS55" s="364" t="n"/>
+      <c r="GT55" s="364" t="n"/>
+      <c r="GU55" s="364" t="n"/>
+      <c r="GV55" s="364" t="n"/>
+      <c r="GW55" s="364" t="n"/>
+      <c r="GX55" s="364" t="n"/>
+      <c r="GY55" s="364" t="n"/>
+      <c r="GZ55" s="364" t="n"/>
+      <c r="HA55" s="364" t="n"/>
+      <c r="HB55" s="364" t="n"/>
+      <c r="HC55" s="364" t="n"/>
+      <c r="HD55" s="364" t="n"/>
+      <c r="HE55" s="364" t="n"/>
+      <c r="HF55" s="364" t="n"/>
+      <c r="HG55" s="364" t="n"/>
+      <c r="HH55" s="364" t="n"/>
+      <c r="HI55" s="364" t="n"/>
+      <c r="HJ55" s="364" t="n"/>
+      <c r="HK55" s="364" t="n"/>
+      <c r="HL55" s="364" t="n"/>
+      <c r="HM55" s="364" t="n"/>
+      <c r="HN55" s="364" t="n"/>
+      <c r="HO55" s="364" t="n"/>
     </row>
     <row r="56" ht="15.75" customHeight="1" s="173">
       <c r="A56" s="156" t="n"/>
       <c r="B56" s="156" t="n"/>
-      <c r="C56" s="156" t="n"/>
-      <c r="D56" s="171" t="n"/>
-      <c r="E56" s="171" t="n"/>
-      <c r="F56" s="156" t="n"/>
+      <c r="C56" s="404" t="n"/>
       <c r="G56" s="172" t="n"/>
       <c r="H56" s="172" t="n"/>
       <c r="I56" s="172" t="n"/>
@@ -17028,10 +17192,7 @@
     <row r="57" ht="15.75" customHeight="1" s="173">
       <c r="A57" s="156" t="n"/>
       <c r="B57" s="156" t="n"/>
-      <c r="C57" s="156" t="n"/>
-      <c r="D57" s="171" t="n"/>
-      <c r="E57" s="171" t="n"/>
-      <c r="F57" s="156" t="n"/>
+      <c r="C57" s="404" t="n"/>
       <c r="G57" s="172" t="n"/>
       <c r="H57" s="172" t="n"/>
       <c r="I57" s="172" t="n"/>
@@ -51225,6 +51386,766 @@
       <c r="GE236" s="172" t="n"/>
       <c r="GF236" s="172" t="n"/>
     </row>
+    <row r="237">
+      <c r="A237" s="156" t="n"/>
+      <c r="B237" s="156" t="n"/>
+      <c r="C237" s="156" t="n"/>
+      <c r="D237" s="171" t="n"/>
+      <c r="E237" s="171" t="n"/>
+      <c r="F237" s="156" t="n"/>
+      <c r="G237" s="172" t="n"/>
+      <c r="H237" s="172" t="n"/>
+      <c r="I237" s="172" t="n"/>
+      <c r="J237" s="172" t="n"/>
+      <c r="K237" s="172" t="n"/>
+      <c r="L237" s="172" t="n"/>
+      <c r="M237" s="172" t="n"/>
+      <c r="N237" s="172" t="n"/>
+      <c r="O237" s="172" t="n"/>
+      <c r="P237" s="172" t="n"/>
+      <c r="Q237" s="172" t="n"/>
+      <c r="R237" s="172" t="n"/>
+      <c r="S237" s="172" t="n"/>
+      <c r="T237" s="172" t="n"/>
+      <c r="U237" s="172" t="n"/>
+      <c r="V237" s="172" t="n"/>
+      <c r="W237" s="172" t="n"/>
+      <c r="X237" s="172" t="n"/>
+      <c r="Y237" s="172" t="n"/>
+      <c r="Z237" s="172" t="n"/>
+      <c r="AA237" s="172" t="n"/>
+      <c r="AB237" s="172" t="n"/>
+      <c r="AC237" s="172" t="n"/>
+      <c r="AD237" s="172" t="n"/>
+      <c r="AE237" s="172" t="n"/>
+      <c r="AF237" s="172" t="n"/>
+      <c r="AG237" s="172" t="n"/>
+      <c r="AH237" s="172" t="n"/>
+      <c r="AI237" s="172" t="n"/>
+      <c r="AJ237" s="172" t="n"/>
+      <c r="AK237" s="172" t="n"/>
+      <c r="AL237" s="172" t="n"/>
+      <c r="AM237" s="172" t="n"/>
+      <c r="AN237" s="172" t="n"/>
+      <c r="AO237" s="172" t="n"/>
+      <c r="AP237" s="172" t="n"/>
+      <c r="AQ237" s="172" t="n"/>
+      <c r="AR237" s="172" t="n"/>
+      <c r="AS237" s="172" t="n"/>
+      <c r="AT237" s="172" t="n"/>
+      <c r="AU237" s="172" t="n"/>
+      <c r="AV237" s="172" t="n"/>
+      <c r="AW237" s="172" t="n"/>
+      <c r="AX237" s="172" t="n"/>
+      <c r="AY237" s="172" t="n"/>
+      <c r="AZ237" s="172" t="n"/>
+      <c r="BA237" s="172" t="n"/>
+      <c r="BB237" s="172" t="n"/>
+      <c r="BC237" s="172" t="n"/>
+      <c r="BD237" s="172" t="n"/>
+      <c r="BE237" s="172" t="n"/>
+      <c r="BF237" s="172" t="n"/>
+      <c r="BG237" s="172" t="n"/>
+      <c r="BH237" s="172" t="n"/>
+      <c r="BI237" s="172" t="n"/>
+      <c r="BJ237" s="172" t="n"/>
+      <c r="BK237" s="172" t="n"/>
+      <c r="BL237" s="172" t="n"/>
+      <c r="BM237" s="172" t="n"/>
+      <c r="BN237" s="172" t="n"/>
+      <c r="BO237" s="172" t="n"/>
+      <c r="BP237" s="172" t="n"/>
+      <c r="BQ237" s="172" t="n"/>
+      <c r="BR237" s="172" t="n"/>
+      <c r="BS237" s="172" t="n"/>
+      <c r="BT237" s="172" t="n"/>
+      <c r="BU237" s="172" t="n"/>
+      <c r="BV237" s="172" t="n"/>
+      <c r="BW237" s="172" t="n"/>
+      <c r="BX237" s="172" t="n"/>
+      <c r="BY237" s="172" t="n"/>
+      <c r="BZ237" s="172" t="n"/>
+      <c r="CA237" s="172" t="n"/>
+      <c r="CB237" s="172" t="n"/>
+      <c r="CC237" s="172" t="n"/>
+      <c r="CD237" s="172" t="n"/>
+      <c r="CE237" s="172" t="n"/>
+      <c r="CF237" s="172" t="n"/>
+      <c r="CG237" s="172" t="n"/>
+      <c r="CH237" s="172" t="n"/>
+      <c r="CI237" s="172" t="n"/>
+      <c r="CJ237" s="172" t="n"/>
+      <c r="CK237" s="172" t="n"/>
+      <c r="CL237" s="172" t="n"/>
+      <c r="CM237" s="172" t="n"/>
+      <c r="CN237" s="172" t="n"/>
+      <c r="CO237" s="172" t="n"/>
+      <c r="CP237" s="172" t="n"/>
+      <c r="CQ237" s="172" t="n"/>
+      <c r="CR237" s="172" t="n"/>
+      <c r="CS237" s="172" t="n"/>
+      <c r="CT237" s="172" t="n"/>
+      <c r="CU237" s="172" t="n"/>
+      <c r="CV237" s="172" t="n"/>
+      <c r="CW237" s="172" t="n"/>
+      <c r="CX237" s="172" t="n"/>
+      <c r="CY237" s="172" t="n"/>
+      <c r="CZ237" s="172" t="n"/>
+      <c r="DA237" s="172" t="n"/>
+      <c r="DB237" s="172" t="n"/>
+      <c r="DC237" s="172" t="n"/>
+      <c r="DD237" s="172" t="n"/>
+      <c r="DE237" s="172" t="n"/>
+      <c r="DF237" s="172" t="n"/>
+      <c r="DG237" s="172" t="n"/>
+      <c r="DH237" s="172" t="n"/>
+      <c r="DI237" s="172" t="n"/>
+      <c r="DJ237" s="172" t="n"/>
+      <c r="DK237" s="172" t="n"/>
+      <c r="DL237" s="172" t="n"/>
+      <c r="DM237" s="172" t="n"/>
+      <c r="DN237" s="172" t="n"/>
+      <c r="DO237" s="172" t="n"/>
+      <c r="DP237" s="172" t="n"/>
+      <c r="DQ237" s="172" t="n"/>
+      <c r="DR237" s="172" t="n"/>
+      <c r="DS237" s="172" t="n"/>
+      <c r="DT237" s="172" t="n"/>
+      <c r="DU237" s="172" t="n"/>
+      <c r="DV237" s="172" t="n"/>
+      <c r="DW237" s="172" t="n"/>
+      <c r="DX237" s="172" t="n"/>
+      <c r="DY237" s="172" t="n"/>
+      <c r="DZ237" s="172" t="n"/>
+      <c r="EA237" s="172" t="n"/>
+      <c r="EB237" s="172" t="n"/>
+      <c r="EC237" s="172" t="n"/>
+      <c r="ED237" s="172" t="n"/>
+      <c r="EE237" s="172" t="n"/>
+      <c r="EF237" s="172" t="n"/>
+      <c r="EG237" s="172" t="n"/>
+      <c r="EH237" s="172" t="n"/>
+      <c r="EI237" s="172" t="n"/>
+      <c r="EJ237" s="172" t="n"/>
+      <c r="EK237" s="172" t="n"/>
+      <c r="EL237" s="172" t="n"/>
+      <c r="EM237" s="172" t="n"/>
+      <c r="EN237" s="172" t="n"/>
+      <c r="EO237" s="172" t="n"/>
+      <c r="EP237" s="172" t="n"/>
+      <c r="EQ237" s="172" t="n"/>
+      <c r="ER237" s="172" t="n"/>
+      <c r="ES237" s="172" t="n"/>
+      <c r="ET237" s="172" t="n"/>
+      <c r="EU237" s="172" t="n"/>
+      <c r="EV237" s="172" t="n"/>
+      <c r="EW237" s="172" t="n"/>
+      <c r="EX237" s="172" t="n"/>
+      <c r="EY237" s="172" t="n"/>
+      <c r="EZ237" s="172" t="n"/>
+      <c r="FA237" s="172" t="n"/>
+      <c r="FB237" s="172" t="n"/>
+      <c r="FC237" s="172" t="n"/>
+      <c r="FD237" s="172" t="n"/>
+      <c r="FE237" s="172" t="n"/>
+      <c r="FF237" s="172" t="n"/>
+      <c r="FG237" s="172" t="n"/>
+      <c r="FH237" s="172" t="n"/>
+      <c r="FI237" s="172" t="n"/>
+      <c r="FJ237" s="172" t="n"/>
+      <c r="FK237" s="172" t="n"/>
+      <c r="FL237" s="172" t="n"/>
+      <c r="FM237" s="172" t="n"/>
+      <c r="FN237" s="172" t="n"/>
+      <c r="FO237" s="172" t="n"/>
+      <c r="FP237" s="172" t="n"/>
+      <c r="FQ237" s="172" t="n"/>
+      <c r="FR237" s="172" t="n"/>
+      <c r="FS237" s="172" t="n"/>
+      <c r="FT237" s="172" t="n"/>
+      <c r="FU237" s="172" t="n"/>
+      <c r="FV237" s="172" t="n"/>
+      <c r="FW237" s="172" t="n"/>
+      <c r="FX237" s="172" t="n"/>
+      <c r="FY237" s="172" t="n"/>
+      <c r="FZ237" s="172" t="n"/>
+      <c r="GA237" s="172" t="n"/>
+      <c r="GB237" s="172" t="n"/>
+      <c r="GC237" s="172" t="n"/>
+      <c r="GD237" s="172" t="n"/>
+      <c r="GE237" s="172" t="n"/>
+      <c r="GF237" s="172" t="n"/>
+    </row>
+    <row r="238">
+      <c r="A238" s="156" t="n"/>
+      <c r="B238" s="156" t="n"/>
+      <c r="C238" s="156" t="n"/>
+      <c r="D238" s="171" t="n"/>
+      <c r="E238" s="171" t="n"/>
+      <c r="F238" s="156" t="n"/>
+      <c r="G238" s="172" t="n"/>
+      <c r="H238" s="172" t="n"/>
+      <c r="I238" s="172" t="n"/>
+      <c r="J238" s="172" t="n"/>
+      <c r="K238" s="172" t="n"/>
+      <c r="L238" s="172" t="n"/>
+      <c r="M238" s="172" t="n"/>
+      <c r="N238" s="172" t="n"/>
+      <c r="O238" s="172" t="n"/>
+      <c r="P238" s="172" t="n"/>
+      <c r="Q238" s="172" t="n"/>
+      <c r="R238" s="172" t="n"/>
+      <c r="S238" s="172" t="n"/>
+      <c r="T238" s="172" t="n"/>
+      <c r="U238" s="172" t="n"/>
+      <c r="V238" s="172" t="n"/>
+      <c r="W238" s="172" t="n"/>
+      <c r="X238" s="172" t="n"/>
+      <c r="Y238" s="172" t="n"/>
+      <c r="Z238" s="172" t="n"/>
+      <c r="AA238" s="172" t="n"/>
+      <c r="AB238" s="172" t="n"/>
+      <c r="AC238" s="172" t="n"/>
+      <c r="AD238" s="172" t="n"/>
+      <c r="AE238" s="172" t="n"/>
+      <c r="AF238" s="172" t="n"/>
+      <c r="AG238" s="172" t="n"/>
+      <c r="AH238" s="172" t="n"/>
+      <c r="AI238" s="172" t="n"/>
+      <c r="AJ238" s="172" t="n"/>
+      <c r="AK238" s="172" t="n"/>
+      <c r="AL238" s="172" t="n"/>
+      <c r="AM238" s="172" t="n"/>
+      <c r="AN238" s="172" t="n"/>
+      <c r="AO238" s="172" t="n"/>
+      <c r="AP238" s="172" t="n"/>
+      <c r="AQ238" s="172" t="n"/>
+      <c r="AR238" s="172" t="n"/>
+      <c r="AS238" s="172" t="n"/>
+      <c r="AT238" s="172" t="n"/>
+      <c r="AU238" s="172" t="n"/>
+      <c r="AV238" s="172" t="n"/>
+      <c r="AW238" s="172" t="n"/>
+      <c r="AX238" s="172" t="n"/>
+      <c r="AY238" s="172" t="n"/>
+      <c r="AZ238" s="172" t="n"/>
+      <c r="BA238" s="172" t="n"/>
+      <c r="BB238" s="172" t="n"/>
+      <c r="BC238" s="172" t="n"/>
+      <c r="BD238" s="172" t="n"/>
+      <c r="BE238" s="172" t="n"/>
+      <c r="BF238" s="172" t="n"/>
+      <c r="BG238" s="172" t="n"/>
+      <c r="BH238" s="172" t="n"/>
+      <c r="BI238" s="172" t="n"/>
+      <c r="BJ238" s="172" t="n"/>
+      <c r="BK238" s="172" t="n"/>
+      <c r="BL238" s="172" t="n"/>
+      <c r="BM238" s="172" t="n"/>
+      <c r="BN238" s="172" t="n"/>
+      <c r="BO238" s="172" t="n"/>
+      <c r="BP238" s="172" t="n"/>
+      <c r="BQ238" s="172" t="n"/>
+      <c r="BR238" s="172" t="n"/>
+      <c r="BS238" s="172" t="n"/>
+      <c r="BT238" s="172" t="n"/>
+      <c r="BU238" s="172" t="n"/>
+      <c r="BV238" s="172" t="n"/>
+      <c r="BW238" s="172" t="n"/>
+      <c r="BX238" s="172" t="n"/>
+      <c r="BY238" s="172" t="n"/>
+      <c r="BZ238" s="172" t="n"/>
+      <c r="CA238" s="172" t="n"/>
+      <c r="CB238" s="172" t="n"/>
+      <c r="CC238" s="172" t="n"/>
+      <c r="CD238" s="172" t="n"/>
+      <c r="CE238" s="172" t="n"/>
+      <c r="CF238" s="172" t="n"/>
+      <c r="CG238" s="172" t="n"/>
+      <c r="CH238" s="172" t="n"/>
+      <c r="CI238" s="172" t="n"/>
+      <c r="CJ238" s="172" t="n"/>
+      <c r="CK238" s="172" t="n"/>
+      <c r="CL238" s="172" t="n"/>
+      <c r="CM238" s="172" t="n"/>
+      <c r="CN238" s="172" t="n"/>
+      <c r="CO238" s="172" t="n"/>
+      <c r="CP238" s="172" t="n"/>
+      <c r="CQ238" s="172" t="n"/>
+      <c r="CR238" s="172" t="n"/>
+      <c r="CS238" s="172" t="n"/>
+      <c r="CT238" s="172" t="n"/>
+      <c r="CU238" s="172" t="n"/>
+      <c r="CV238" s="172" t="n"/>
+      <c r="CW238" s="172" t="n"/>
+      <c r="CX238" s="172" t="n"/>
+      <c r="CY238" s="172" t="n"/>
+      <c r="CZ238" s="172" t="n"/>
+      <c r="DA238" s="172" t="n"/>
+      <c r="DB238" s="172" t="n"/>
+      <c r="DC238" s="172" t="n"/>
+      <c r="DD238" s="172" t="n"/>
+      <c r="DE238" s="172" t="n"/>
+      <c r="DF238" s="172" t="n"/>
+      <c r="DG238" s="172" t="n"/>
+      <c r="DH238" s="172" t="n"/>
+      <c r="DI238" s="172" t="n"/>
+      <c r="DJ238" s="172" t="n"/>
+      <c r="DK238" s="172" t="n"/>
+      <c r="DL238" s="172" t="n"/>
+      <c r="DM238" s="172" t="n"/>
+      <c r="DN238" s="172" t="n"/>
+      <c r="DO238" s="172" t="n"/>
+      <c r="DP238" s="172" t="n"/>
+      <c r="DQ238" s="172" t="n"/>
+      <c r="DR238" s="172" t="n"/>
+      <c r="DS238" s="172" t="n"/>
+      <c r="DT238" s="172" t="n"/>
+      <c r="DU238" s="172" t="n"/>
+      <c r="DV238" s="172" t="n"/>
+      <c r="DW238" s="172" t="n"/>
+      <c r="DX238" s="172" t="n"/>
+      <c r="DY238" s="172" t="n"/>
+      <c r="DZ238" s="172" t="n"/>
+      <c r="EA238" s="172" t="n"/>
+      <c r="EB238" s="172" t="n"/>
+      <c r="EC238" s="172" t="n"/>
+      <c r="ED238" s="172" t="n"/>
+      <c r="EE238" s="172" t="n"/>
+      <c r="EF238" s="172" t="n"/>
+      <c r="EG238" s="172" t="n"/>
+      <c r="EH238" s="172" t="n"/>
+      <c r="EI238" s="172" t="n"/>
+      <c r="EJ238" s="172" t="n"/>
+      <c r="EK238" s="172" t="n"/>
+      <c r="EL238" s="172" t="n"/>
+      <c r="EM238" s="172" t="n"/>
+      <c r="EN238" s="172" t="n"/>
+      <c r="EO238" s="172" t="n"/>
+      <c r="EP238" s="172" t="n"/>
+      <c r="EQ238" s="172" t="n"/>
+      <c r="ER238" s="172" t="n"/>
+      <c r="ES238" s="172" t="n"/>
+      <c r="ET238" s="172" t="n"/>
+      <c r="EU238" s="172" t="n"/>
+      <c r="EV238" s="172" t="n"/>
+      <c r="EW238" s="172" t="n"/>
+      <c r="EX238" s="172" t="n"/>
+      <c r="EY238" s="172" t="n"/>
+      <c r="EZ238" s="172" t="n"/>
+      <c r="FA238" s="172" t="n"/>
+      <c r="FB238" s="172" t="n"/>
+      <c r="FC238" s="172" t="n"/>
+      <c r="FD238" s="172" t="n"/>
+      <c r="FE238" s="172" t="n"/>
+      <c r="FF238" s="172" t="n"/>
+      <c r="FG238" s="172" t="n"/>
+      <c r="FH238" s="172" t="n"/>
+      <c r="FI238" s="172" t="n"/>
+      <c r="FJ238" s="172" t="n"/>
+      <c r="FK238" s="172" t="n"/>
+      <c r="FL238" s="172" t="n"/>
+      <c r="FM238" s="172" t="n"/>
+      <c r="FN238" s="172" t="n"/>
+      <c r="FO238" s="172" t="n"/>
+      <c r="FP238" s="172" t="n"/>
+      <c r="FQ238" s="172" t="n"/>
+      <c r="FR238" s="172" t="n"/>
+      <c r="FS238" s="172" t="n"/>
+      <c r="FT238" s="172" t="n"/>
+      <c r="FU238" s="172" t="n"/>
+      <c r="FV238" s="172" t="n"/>
+      <c r="FW238" s="172" t="n"/>
+      <c r="FX238" s="172" t="n"/>
+      <c r="FY238" s="172" t="n"/>
+      <c r="FZ238" s="172" t="n"/>
+      <c r="GA238" s="172" t="n"/>
+      <c r="GB238" s="172" t="n"/>
+      <c r="GC238" s="172" t="n"/>
+      <c r="GD238" s="172" t="n"/>
+      <c r="GE238" s="172" t="n"/>
+      <c r="GF238" s="172" t="n"/>
+    </row>
+    <row r="239">
+      <c r="A239" s="156" t="n"/>
+      <c r="B239" s="156" t="n"/>
+      <c r="C239" s="156" t="n"/>
+      <c r="D239" s="171" t="n"/>
+      <c r="E239" s="171" t="n"/>
+      <c r="F239" s="156" t="n"/>
+      <c r="G239" s="172" t="n"/>
+      <c r="H239" s="172" t="n"/>
+      <c r="I239" s="172" t="n"/>
+      <c r="J239" s="172" t="n"/>
+      <c r="K239" s="172" t="n"/>
+      <c r="L239" s="172" t="n"/>
+      <c r="M239" s="172" t="n"/>
+      <c r="N239" s="172" t="n"/>
+      <c r="O239" s="172" t="n"/>
+      <c r="P239" s="172" t="n"/>
+      <c r="Q239" s="172" t="n"/>
+      <c r="R239" s="172" t="n"/>
+      <c r="S239" s="172" t="n"/>
+      <c r="T239" s="172" t="n"/>
+      <c r="U239" s="172" t="n"/>
+      <c r="V239" s="172" t="n"/>
+      <c r="W239" s="172" t="n"/>
+      <c r="X239" s="172" t="n"/>
+      <c r="Y239" s="172" t="n"/>
+      <c r="Z239" s="172" t="n"/>
+      <c r="AA239" s="172" t="n"/>
+      <c r="AB239" s="172" t="n"/>
+      <c r="AC239" s="172" t="n"/>
+      <c r="AD239" s="172" t="n"/>
+      <c r="AE239" s="172" t="n"/>
+      <c r="AF239" s="172" t="n"/>
+      <c r="AG239" s="172" t="n"/>
+      <c r="AH239" s="172" t="n"/>
+      <c r="AI239" s="172" t="n"/>
+      <c r="AJ239" s="172" t="n"/>
+      <c r="AK239" s="172" t="n"/>
+      <c r="AL239" s="172" t="n"/>
+      <c r="AM239" s="172" t="n"/>
+      <c r="AN239" s="172" t="n"/>
+      <c r="AO239" s="172" t="n"/>
+      <c r="AP239" s="172" t="n"/>
+      <c r="AQ239" s="172" t="n"/>
+      <c r="AR239" s="172" t="n"/>
+      <c r="AS239" s="172" t="n"/>
+      <c r="AT239" s="172" t="n"/>
+      <c r="AU239" s="172" t="n"/>
+      <c r="AV239" s="172" t="n"/>
+      <c r="AW239" s="172" t="n"/>
+      <c r="AX239" s="172" t="n"/>
+      <c r="AY239" s="172" t="n"/>
+      <c r="AZ239" s="172" t="n"/>
+      <c r="BA239" s="172" t="n"/>
+      <c r="BB239" s="172" t="n"/>
+      <c r="BC239" s="172" t="n"/>
+      <c r="BD239" s="172" t="n"/>
+      <c r="BE239" s="172" t="n"/>
+      <c r="BF239" s="172" t="n"/>
+      <c r="BG239" s="172" t="n"/>
+      <c r="BH239" s="172" t="n"/>
+      <c r="BI239" s="172" t="n"/>
+      <c r="BJ239" s="172" t="n"/>
+      <c r="BK239" s="172" t="n"/>
+      <c r="BL239" s="172" t="n"/>
+      <c r="BM239" s="172" t="n"/>
+      <c r="BN239" s="172" t="n"/>
+      <c r="BO239" s="172" t="n"/>
+      <c r="BP239" s="172" t="n"/>
+      <c r="BQ239" s="172" t="n"/>
+      <c r="BR239" s="172" t="n"/>
+      <c r="BS239" s="172" t="n"/>
+      <c r="BT239" s="172" t="n"/>
+      <c r="BU239" s="172" t="n"/>
+      <c r="BV239" s="172" t="n"/>
+      <c r="BW239" s="172" t="n"/>
+      <c r="BX239" s="172" t="n"/>
+      <c r="BY239" s="172" t="n"/>
+      <c r="BZ239" s="172" t="n"/>
+      <c r="CA239" s="172" t="n"/>
+      <c r="CB239" s="172" t="n"/>
+      <c r="CC239" s="172" t="n"/>
+      <c r="CD239" s="172" t="n"/>
+      <c r="CE239" s="172" t="n"/>
+      <c r="CF239" s="172" t="n"/>
+      <c r="CG239" s="172" t="n"/>
+      <c r="CH239" s="172" t="n"/>
+      <c r="CI239" s="172" t="n"/>
+      <c r="CJ239" s="172" t="n"/>
+      <c r="CK239" s="172" t="n"/>
+      <c r="CL239" s="172" t="n"/>
+      <c r="CM239" s="172" t="n"/>
+      <c r="CN239" s="172" t="n"/>
+      <c r="CO239" s="172" t="n"/>
+      <c r="CP239" s="172" t="n"/>
+      <c r="CQ239" s="172" t="n"/>
+      <c r="CR239" s="172" t="n"/>
+      <c r="CS239" s="172" t="n"/>
+      <c r="CT239" s="172" t="n"/>
+      <c r="CU239" s="172" t="n"/>
+      <c r="CV239" s="172" t="n"/>
+      <c r="CW239" s="172" t="n"/>
+      <c r="CX239" s="172" t="n"/>
+      <c r="CY239" s="172" t="n"/>
+      <c r="CZ239" s="172" t="n"/>
+      <c r="DA239" s="172" t="n"/>
+      <c r="DB239" s="172" t="n"/>
+      <c r="DC239" s="172" t="n"/>
+      <c r="DD239" s="172" t="n"/>
+      <c r="DE239" s="172" t="n"/>
+      <c r="DF239" s="172" t="n"/>
+      <c r="DG239" s="172" t="n"/>
+      <c r="DH239" s="172" t="n"/>
+      <c r="DI239" s="172" t="n"/>
+      <c r="DJ239" s="172" t="n"/>
+      <c r="DK239" s="172" t="n"/>
+      <c r="DL239" s="172" t="n"/>
+      <c r="DM239" s="172" t="n"/>
+      <c r="DN239" s="172" t="n"/>
+      <c r="DO239" s="172" t="n"/>
+      <c r="DP239" s="172" t="n"/>
+      <c r="DQ239" s="172" t="n"/>
+      <c r="DR239" s="172" t="n"/>
+      <c r="DS239" s="172" t="n"/>
+      <c r="DT239" s="172" t="n"/>
+      <c r="DU239" s="172" t="n"/>
+      <c r="DV239" s="172" t="n"/>
+      <c r="DW239" s="172" t="n"/>
+      <c r="DX239" s="172" t="n"/>
+      <c r="DY239" s="172" t="n"/>
+      <c r="DZ239" s="172" t="n"/>
+      <c r="EA239" s="172" t="n"/>
+      <c r="EB239" s="172" t="n"/>
+      <c r="EC239" s="172" t="n"/>
+      <c r="ED239" s="172" t="n"/>
+      <c r="EE239" s="172" t="n"/>
+      <c r="EF239" s="172" t="n"/>
+      <c r="EG239" s="172" t="n"/>
+      <c r="EH239" s="172" t="n"/>
+      <c r="EI239" s="172" t="n"/>
+      <c r="EJ239" s="172" t="n"/>
+      <c r="EK239" s="172" t="n"/>
+      <c r="EL239" s="172" t="n"/>
+      <c r="EM239" s="172" t="n"/>
+      <c r="EN239" s="172" t="n"/>
+      <c r="EO239" s="172" t="n"/>
+      <c r="EP239" s="172" t="n"/>
+      <c r="EQ239" s="172" t="n"/>
+      <c r="ER239" s="172" t="n"/>
+      <c r="ES239" s="172" t="n"/>
+      <c r="ET239" s="172" t="n"/>
+      <c r="EU239" s="172" t="n"/>
+      <c r="EV239" s="172" t="n"/>
+      <c r="EW239" s="172" t="n"/>
+      <c r="EX239" s="172" t="n"/>
+      <c r="EY239" s="172" t="n"/>
+      <c r="EZ239" s="172" t="n"/>
+      <c r="FA239" s="172" t="n"/>
+      <c r="FB239" s="172" t="n"/>
+      <c r="FC239" s="172" t="n"/>
+      <c r="FD239" s="172" t="n"/>
+      <c r="FE239" s="172" t="n"/>
+      <c r="FF239" s="172" t="n"/>
+      <c r="FG239" s="172" t="n"/>
+      <c r="FH239" s="172" t="n"/>
+      <c r="FI239" s="172" t="n"/>
+      <c r="FJ239" s="172" t="n"/>
+      <c r="FK239" s="172" t="n"/>
+      <c r="FL239" s="172" t="n"/>
+      <c r="FM239" s="172" t="n"/>
+      <c r="FN239" s="172" t="n"/>
+      <c r="FO239" s="172" t="n"/>
+      <c r="FP239" s="172" t="n"/>
+      <c r="FQ239" s="172" t="n"/>
+      <c r="FR239" s="172" t="n"/>
+      <c r="FS239" s="172" t="n"/>
+      <c r="FT239" s="172" t="n"/>
+      <c r="FU239" s="172" t="n"/>
+      <c r="FV239" s="172" t="n"/>
+      <c r="FW239" s="172" t="n"/>
+      <c r="FX239" s="172" t="n"/>
+      <c r="FY239" s="172" t="n"/>
+      <c r="FZ239" s="172" t="n"/>
+      <c r="GA239" s="172" t="n"/>
+      <c r="GB239" s="172" t="n"/>
+      <c r="GC239" s="172" t="n"/>
+      <c r="GD239" s="172" t="n"/>
+      <c r="GE239" s="172" t="n"/>
+      <c r="GF239" s="172" t="n"/>
+    </row>
+    <row r="240">
+      <c r="A240" s="156" t="n"/>
+      <c r="B240" s="156" t="n"/>
+      <c r="C240" s="156" t="n"/>
+      <c r="D240" s="171" t="n"/>
+      <c r="E240" s="171" t="n"/>
+      <c r="F240" s="156" t="n"/>
+      <c r="G240" s="172" t="n"/>
+      <c r="H240" s="172" t="n"/>
+      <c r="I240" s="172" t="n"/>
+      <c r="J240" s="172" t="n"/>
+      <c r="K240" s="172" t="n"/>
+      <c r="L240" s="172" t="n"/>
+      <c r="M240" s="172" t="n"/>
+      <c r="N240" s="172" t="n"/>
+      <c r="O240" s="172" t="n"/>
+      <c r="P240" s="172" t="n"/>
+      <c r="Q240" s="172" t="n"/>
+      <c r="R240" s="172" t="n"/>
+      <c r="S240" s="172" t="n"/>
+      <c r="T240" s="172" t="n"/>
+      <c r="U240" s="172" t="n"/>
+      <c r="V240" s="172" t="n"/>
+      <c r="W240" s="172" t="n"/>
+      <c r="X240" s="172" t="n"/>
+      <c r="Y240" s="172" t="n"/>
+      <c r="Z240" s="172" t="n"/>
+      <c r="AA240" s="172" t="n"/>
+      <c r="AB240" s="172" t="n"/>
+      <c r="AC240" s="172" t="n"/>
+      <c r="AD240" s="172" t="n"/>
+      <c r="AE240" s="172" t="n"/>
+      <c r="AF240" s="172" t="n"/>
+      <c r="AG240" s="172" t="n"/>
+      <c r="AH240" s="172" t="n"/>
+      <c r="AI240" s="172" t="n"/>
+      <c r="AJ240" s="172" t="n"/>
+      <c r="AK240" s="172" t="n"/>
+      <c r="AL240" s="172" t="n"/>
+      <c r="AM240" s="172" t="n"/>
+      <c r="AN240" s="172" t="n"/>
+      <c r="AO240" s="172" t="n"/>
+      <c r="AP240" s="172" t="n"/>
+      <c r="AQ240" s="172" t="n"/>
+      <c r="AR240" s="172" t="n"/>
+      <c r="AS240" s="172" t="n"/>
+      <c r="AT240" s="172" t="n"/>
+      <c r="AU240" s="172" t="n"/>
+      <c r="AV240" s="172" t="n"/>
+      <c r="AW240" s="172" t="n"/>
+      <c r="AX240" s="172" t="n"/>
+      <c r="AY240" s="172" t="n"/>
+      <c r="AZ240" s="172" t="n"/>
+      <c r="BA240" s="172" t="n"/>
+      <c r="BB240" s="172" t="n"/>
+      <c r="BC240" s="172" t="n"/>
+      <c r="BD240" s="172" t="n"/>
+      <c r="BE240" s="172" t="n"/>
+      <c r="BF240" s="172" t="n"/>
+      <c r="BG240" s="172" t="n"/>
+      <c r="BH240" s="172" t="n"/>
+      <c r="BI240" s="172" t="n"/>
+      <c r="BJ240" s="172" t="n"/>
+      <c r="BK240" s="172" t="n"/>
+      <c r="BL240" s="172" t="n"/>
+      <c r="BM240" s="172" t="n"/>
+      <c r="BN240" s="172" t="n"/>
+      <c r="BO240" s="172" t="n"/>
+      <c r="BP240" s="172" t="n"/>
+      <c r="BQ240" s="172" t="n"/>
+      <c r="BR240" s="172" t="n"/>
+      <c r="BS240" s="172" t="n"/>
+      <c r="BT240" s="172" t="n"/>
+      <c r="BU240" s="172" t="n"/>
+      <c r="BV240" s="172" t="n"/>
+      <c r="BW240" s="172" t="n"/>
+      <c r="BX240" s="172" t="n"/>
+      <c r="BY240" s="172" t="n"/>
+      <c r="BZ240" s="172" t="n"/>
+      <c r="CA240" s="172" t="n"/>
+      <c r="CB240" s="172" t="n"/>
+      <c r="CC240" s="172" t="n"/>
+      <c r="CD240" s="172" t="n"/>
+      <c r="CE240" s="172" t="n"/>
+      <c r="CF240" s="172" t="n"/>
+      <c r="CG240" s="172" t="n"/>
+      <c r="CH240" s="172" t="n"/>
+      <c r="CI240" s="172" t="n"/>
+      <c r="CJ240" s="172" t="n"/>
+      <c r="CK240" s="172" t="n"/>
+      <c r="CL240" s="172" t="n"/>
+      <c r="CM240" s="172" t="n"/>
+      <c r="CN240" s="172" t="n"/>
+      <c r="CO240" s="172" t="n"/>
+      <c r="CP240" s="172" t="n"/>
+      <c r="CQ240" s="172" t="n"/>
+      <c r="CR240" s="172" t="n"/>
+      <c r="CS240" s="172" t="n"/>
+      <c r="CT240" s="172" t="n"/>
+      <c r="CU240" s="172" t="n"/>
+      <c r="CV240" s="172" t="n"/>
+      <c r="CW240" s="172" t="n"/>
+      <c r="CX240" s="172" t="n"/>
+      <c r="CY240" s="172" t="n"/>
+      <c r="CZ240" s="172" t="n"/>
+      <c r="DA240" s="172" t="n"/>
+      <c r="DB240" s="172" t="n"/>
+      <c r="DC240" s="172" t="n"/>
+      <c r="DD240" s="172" t="n"/>
+      <c r="DE240" s="172" t="n"/>
+      <c r="DF240" s="172" t="n"/>
+      <c r="DG240" s="172" t="n"/>
+      <c r="DH240" s="172" t="n"/>
+      <c r="DI240" s="172" t="n"/>
+      <c r="DJ240" s="172" t="n"/>
+      <c r="DK240" s="172" t="n"/>
+      <c r="DL240" s="172" t="n"/>
+      <c r="DM240" s="172" t="n"/>
+      <c r="DN240" s="172" t="n"/>
+      <c r="DO240" s="172" t="n"/>
+      <c r="DP240" s="172" t="n"/>
+      <c r="DQ240" s="172" t="n"/>
+      <c r="DR240" s="172" t="n"/>
+      <c r="DS240" s="172" t="n"/>
+      <c r="DT240" s="172" t="n"/>
+      <c r="DU240" s="172" t="n"/>
+      <c r="DV240" s="172" t="n"/>
+      <c r="DW240" s="172" t="n"/>
+      <c r="DX240" s="172" t="n"/>
+      <c r="DY240" s="172" t="n"/>
+      <c r="DZ240" s="172" t="n"/>
+      <c r="EA240" s="172" t="n"/>
+      <c r="EB240" s="172" t="n"/>
+      <c r="EC240" s="172" t="n"/>
+      <c r="ED240" s="172" t="n"/>
+      <c r="EE240" s="172" t="n"/>
+      <c r="EF240" s="172" t="n"/>
+      <c r="EG240" s="172" t="n"/>
+      <c r="EH240" s="172" t="n"/>
+      <c r="EI240" s="172" t="n"/>
+      <c r="EJ240" s="172" t="n"/>
+      <c r="EK240" s="172" t="n"/>
+      <c r="EL240" s="172" t="n"/>
+      <c r="EM240" s="172" t="n"/>
+      <c r="EN240" s="172" t="n"/>
+      <c r="EO240" s="172" t="n"/>
+      <c r="EP240" s="172" t="n"/>
+      <c r="EQ240" s="172" t="n"/>
+      <c r="ER240" s="172" t="n"/>
+      <c r="ES240" s="172" t="n"/>
+      <c r="ET240" s="172" t="n"/>
+      <c r="EU240" s="172" t="n"/>
+      <c r="EV240" s="172" t="n"/>
+      <c r="EW240" s="172" t="n"/>
+      <c r="EX240" s="172" t="n"/>
+      <c r="EY240" s="172" t="n"/>
+      <c r="EZ240" s="172" t="n"/>
+      <c r="FA240" s="172" t="n"/>
+      <c r="FB240" s="172" t="n"/>
+      <c r="FC240" s="172" t="n"/>
+      <c r="FD240" s="172" t="n"/>
+      <c r="FE240" s="172" t="n"/>
+      <c r="FF240" s="172" t="n"/>
+      <c r="FG240" s="172" t="n"/>
+      <c r="FH240" s="172" t="n"/>
+      <c r="FI240" s="172" t="n"/>
+      <c r="FJ240" s="172" t="n"/>
+      <c r="FK240" s="172" t="n"/>
+      <c r="FL240" s="172" t="n"/>
+      <c r="FM240" s="172" t="n"/>
+      <c r="FN240" s="172" t="n"/>
+      <c r="FO240" s="172" t="n"/>
+      <c r="FP240" s="172" t="n"/>
+      <c r="FQ240" s="172" t="n"/>
+      <c r="FR240" s="172" t="n"/>
+      <c r="FS240" s="172" t="n"/>
+      <c r="FT240" s="172" t="n"/>
+      <c r="FU240" s="172" t="n"/>
+      <c r="FV240" s="172" t="n"/>
+      <c r="FW240" s="172" t="n"/>
+      <c r="FX240" s="172" t="n"/>
+      <c r="FY240" s="172" t="n"/>
+      <c r="FZ240" s="172" t="n"/>
+      <c r="GA240" s="172" t="n"/>
+      <c r="GB240" s="172" t="n"/>
+      <c r="GC240" s="172" t="n"/>
+      <c r="GD240" s="172" t="n"/>
+      <c r="GE240" s="172" t="n"/>
+      <c r="GF240" s="172" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="58">
     <mergeCell ref="C48:F48"/>
